--- a/artfynd/A 40737-2024 artfynd.xlsx
+++ b/artfynd/A 40737-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087311</v>
+        <v>121087281</v>
       </c>
       <c r="B2" t="n">
-        <v>91031</v>
+        <v>74705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542016</v>
+        <v>541693</v>
       </c>
       <c r="R2" t="n">
-        <v>7208338</v>
+        <v>7208064</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>S. brevispora s.str</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,21 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -807,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087281</v>
+        <v>121087323</v>
       </c>
       <c r="B3" t="n">
-        <v>74705</v>
+        <v>57364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541693</v>
+        <v>541897</v>
       </c>
       <c r="R3" t="n">
-        <v>7208064</v>
+        <v>7208135</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087278</v>
+        <v>121087349</v>
       </c>
       <c r="B4" t="n">
-        <v>97031</v>
+        <v>57348</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541725</v>
+        <v>541836</v>
       </c>
       <c r="R4" t="n">
-        <v>7208037</v>
+        <v>7207921</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121087323</v>
+        <v>121087318</v>
       </c>
       <c r="B5" t="n">
-        <v>57364</v>
+        <v>57348</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1076,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541897</v>
+        <v>541944</v>
       </c>
       <c r="R5" t="n">
-        <v>7208135</v>
+        <v>7208213</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1111,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087349</v>
+        <v>121087336</v>
       </c>
       <c r="B6" t="n">
         <v>57348</v>
@@ -1184,7 +1174,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541836</v>
+        <v>541811</v>
       </c>
       <c r="R6" t="n">
-        <v>7207921</v>
+        <v>7208016</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087318</v>
+        <v>121087311</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>91031</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,43 +1267,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541944</v>
+        <v>542016</v>
       </c>
       <c r="R7" t="n">
-        <v>7208213</v>
+        <v>7208338</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1345,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>S. brevispora s.str</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,6 +1356,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121087336</v>
+        <v>121087278</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>97031</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,43 +1399,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541811</v>
+        <v>541725</v>
       </c>
       <c r="R8" t="n">
-        <v>7208016</v>
+        <v>7208037</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2936,10 +2936,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087356</v>
+        <v>121087329</v>
       </c>
       <c r="B21" t="n">
-        <v>82382</v>
+        <v>90687</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541832</v>
+        <v>541819</v>
       </c>
       <c r="R21" t="n">
-        <v>7207849</v>
+        <v>7208041</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,10 +3048,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087329</v>
+        <v>121087356</v>
       </c>
       <c r="B22" t="n">
-        <v>90687</v>
+        <v>82382</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,21 +3064,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541819</v>
+        <v>541832</v>
       </c>
       <c r="R22" t="n">
-        <v>7208041</v>
+        <v>7207849</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4638,10 +4638,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121087313</v>
+        <v>121087275</v>
       </c>
       <c r="B35" t="n">
-        <v>79680</v>
+        <v>57348</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4654,34 +4654,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542053</v>
+        <v>541756</v>
       </c>
       <c r="R35" t="n">
-        <v>7208323</v>
+        <v>7208000</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4713,7 +4718,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4723,7 +4728,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4750,7 +4755,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121087275</v>
+        <v>121087346</v>
       </c>
       <c r="B36" t="n">
         <v>57348</v>
@@ -4786,7 +4791,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4795,10 +4800,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541756</v>
+        <v>541837</v>
       </c>
       <c r="R36" t="n">
-        <v>7208000</v>
+        <v>7207939</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4830,7 +4835,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4840,7 +4845,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4867,7 +4872,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121087346</v>
+        <v>121087286</v>
       </c>
       <c r="B37" t="n">
         <v>57348</v>
@@ -4912,10 +4917,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541837</v>
+        <v>541670</v>
       </c>
       <c r="R37" t="n">
-        <v>7207939</v>
+        <v>7208095</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4947,7 +4952,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4957,7 +4962,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4984,10 +4989,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121087286</v>
+        <v>121087313</v>
       </c>
       <c r="B38" t="n">
-        <v>57348</v>
+        <v>79680</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5000,39 +5005,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541670</v>
+        <v>542053</v>
       </c>
       <c r="R38" t="n">
-        <v>7208095</v>
+        <v>7208323</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5709,10 +5709,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121087332</v>
+        <v>121087351</v>
       </c>
       <c r="B44" t="n">
-        <v>78598</v>
+        <v>57348</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5725,34 +5725,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541817</v>
+        <v>541838</v>
       </c>
       <c r="R44" t="n">
-        <v>7208031</v>
+        <v>7207903</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5784,7 +5789,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5794,7 +5799,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5821,10 +5826,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121087341</v>
+        <v>121087342</v>
       </c>
       <c r="B45" t="n">
-        <v>78598</v>
+        <v>79708</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5833,25 +5838,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5933,7 +5938,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121087317</v>
+        <v>121087341</v>
       </c>
       <c r="B46" t="n">
         <v>78598</v>
@@ -5973,10 +5978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541984</v>
+        <v>541840</v>
       </c>
       <c r="R46" t="n">
-        <v>7208289</v>
+        <v>7207901</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6008,7 +6013,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6018,7 +6023,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6045,10 +6050,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121087342</v>
+        <v>121087317</v>
       </c>
       <c r="B47" t="n">
-        <v>79708</v>
+        <v>78598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6057,25 +6062,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6085,10 +6090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541840</v>
+        <v>541984</v>
       </c>
       <c r="R47" t="n">
-        <v>7207901</v>
+        <v>7208289</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6120,7 +6125,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6130,7 +6135,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6157,10 +6162,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121087351</v>
+        <v>121087332</v>
       </c>
       <c r="B48" t="n">
-        <v>57348</v>
+        <v>78598</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6173,39 +6178,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541838</v>
+        <v>541817</v>
       </c>
       <c r="R48" t="n">
-        <v>7207903</v>
+        <v>7208031</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -8060,10 +8060,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121087316</v>
+        <v>121087334</v>
       </c>
       <c r="B64" t="n">
-        <v>90683</v>
+        <v>57348</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8076,34 +8076,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541984</v>
+        <v>541801</v>
       </c>
       <c r="R64" t="n">
-        <v>7208289</v>
+        <v>7208005</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8135,7 +8140,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8145,7 +8150,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8172,10 +8177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121087334</v>
+        <v>121087316</v>
       </c>
       <c r="B65" t="n">
-        <v>57348</v>
+        <v>90683</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8188,39 +8193,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541801</v>
+        <v>541984</v>
       </c>
       <c r="R65" t="n">
-        <v>7208005</v>
+        <v>7208289</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8755,10 +8755,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121087279</v>
+        <v>121087344</v>
       </c>
       <c r="B70" t="n">
-        <v>78680</v>
+        <v>77535</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8771,21 +8771,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>864</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541703</v>
+        <v>541846</v>
       </c>
       <c r="R70" t="n">
-        <v>7208051</v>
+        <v>7207904</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8867,10 +8867,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121087352</v>
+        <v>121087279</v>
       </c>
       <c r="B71" t="n">
-        <v>78598</v>
+        <v>78680</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8883,21 +8883,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541827</v>
+        <v>541703</v>
       </c>
       <c r="R71" t="n">
-        <v>7207856</v>
+        <v>7208051</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8979,10 +8979,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121087344</v>
+        <v>121087352</v>
       </c>
       <c r="B72" t="n">
-        <v>77535</v>
+        <v>78598</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8995,21 +8995,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9019,10 +9019,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541846</v>
+        <v>541827</v>
       </c>
       <c r="R72" t="n">
-        <v>7207904</v>
+        <v>7207856</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 40737-2024 artfynd.xlsx
+++ b/artfynd/A 40737-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087281</v>
+        <v>121087322</v>
       </c>
       <c r="B2" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541693</v>
+        <v>541931</v>
       </c>
       <c r="R2" t="n">
-        <v>7208064</v>
+        <v>7208192</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087323</v>
+        <v>121087352</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541897</v>
+        <v>541827</v>
       </c>
       <c r="R3" t="n">
-        <v>7208135</v>
+        <v>7207856</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +902,7 @@
         <v>121087349</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121087318</v>
+        <v>121087348</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541944</v>
+        <v>541837</v>
       </c>
       <c r="R5" t="n">
-        <v>7208213</v>
+        <v>7207922</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087336</v>
+        <v>121086337</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,24 +1167,27 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541811</v>
+        <v>541917</v>
       </c>
       <c r="R6" t="n">
-        <v>7208016</v>
+        <v>7208182</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1226,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,26 +1242,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087311</v>
+        <v>121087351</v>
       </c>
       <c r="B7" t="n">
-        <v>91031</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,38 +1285,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542016</v>
+        <v>541838</v>
       </c>
       <c r="R7" t="n">
-        <v>7208338</v>
+        <v>7207903</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>S. brevispora s.str</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,21 +1374,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1387,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121087278</v>
+        <v>121087286</v>
       </c>
       <c r="B8" t="n">
-        <v>97031</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,38 +1402,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541725</v>
+        <v>541670</v>
       </c>
       <c r="R8" t="n">
-        <v>7208037</v>
+        <v>7208095</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1462,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087343</v>
+        <v>121086343</v>
       </c>
       <c r="B9" t="n">
-        <v>82382</v>
+        <v>90693</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,37 +1523,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541847</v>
+        <v>541969</v>
       </c>
       <c r="R9" t="n">
-        <v>7207905</v>
+        <v>7208261</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1585,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1595,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,28 +1609,54 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087355</v>
+        <v>121087310</v>
       </c>
       <c r="B10" t="n">
-        <v>77939</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,25 +1665,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>498</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541834</v>
+        <v>542016</v>
       </c>
       <c r="R10" t="n">
-        <v>7207850</v>
+        <v>7208334</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1686,7 +1728,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1738,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121086336</v>
+        <v>121087326</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,45 +1781,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541937</v>
+        <v>541877</v>
       </c>
       <c r="R11" t="n">
-        <v>7208222</v>
+        <v>7208115</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1806,7 +1840,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,12 +1850,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,46 +1861,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121087315</v>
+        <v>121087320</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1884,39 +1893,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542012</v>
+        <v>541956</v>
       </c>
       <c r="R12" t="n">
-        <v>7208299</v>
+        <v>7208191</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1948,7 +1952,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,10 +1989,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121087335</v>
+        <v>121087355</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>77942</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,43 +2001,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541794</v>
+        <v>541834</v>
       </c>
       <c r="R13" t="n">
-        <v>7208008</v>
+        <v>7207850</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2065,7 +2064,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2074,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,10 +2101,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121087354</v>
+        <v>121087280</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,39 +2117,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541832</v>
+        <v>541704</v>
       </c>
       <c r="R14" t="n">
-        <v>7207855</v>
+        <v>7208050</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2182,7 +2176,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2192,7 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,10 +2213,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121087237</v>
+        <v>121087339</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2253,27 +2247,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542031</v>
+        <v>541843</v>
       </c>
       <c r="R15" t="n">
-        <v>7208267</v>
+        <v>7207891</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2302,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,7 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,22 +2318,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121087327</v>
+        <v>121087346</v>
       </c>
       <c r="B16" t="n">
-        <v>57501</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2355,26 +2346,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2383,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541871</v>
+        <v>541837</v>
       </c>
       <c r="R16" t="n">
-        <v>7208138</v>
+        <v>7207939</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2418,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2428,7 +2420,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2455,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121087337</v>
+        <v>121087287</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2471,34 +2463,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541811</v>
+        <v>541743</v>
       </c>
       <c r="R17" t="n">
-        <v>7208016</v>
+        <v>7208173</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2530,7 +2527,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2540,7 +2537,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2567,10 +2564,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087310</v>
+        <v>121087309</v>
       </c>
       <c r="B18" t="n">
-        <v>90687</v>
+        <v>90983</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,21 +2580,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2610,7 +2607,7 @@
         <v>542016</v>
       </c>
       <c r="R18" t="n">
-        <v>7208334</v>
+        <v>7208333</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2679,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087339</v>
+        <v>121087316</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2695,39 +2692,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541843</v>
+        <v>541984</v>
       </c>
       <c r="R19" t="n">
-        <v>7207891</v>
+        <v>7208289</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2759,7 +2751,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2769,7 +2761,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2796,10 +2788,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121086337</v>
+        <v>121087345</v>
       </c>
       <c r="B20" t="n">
-        <v>57348</v>
+        <v>74708</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2812,45 +2804,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541917</v>
+        <v>541847</v>
       </c>
       <c r="R20" t="n">
-        <v>7208182</v>
+        <v>7207903</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2879,7 +2863,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2889,12 +2873,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,41 +2884,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087329</v>
+        <v>121087312</v>
       </c>
       <c r="B21" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,34 +2916,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541819</v>
+        <v>542080</v>
       </c>
       <c r="R21" t="n">
-        <v>7208041</v>
+        <v>7208265</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3011,7 +2984,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3021,7 +2994,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3048,10 +3021,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087356</v>
+        <v>121087329</v>
       </c>
       <c r="B22" t="n">
-        <v>82382</v>
+        <v>90697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,21 +3037,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3088,10 +3061,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541832</v>
+        <v>541819</v>
       </c>
       <c r="R22" t="n">
-        <v>7207849</v>
+        <v>7208041</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3123,7 +3096,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3133,7 +3106,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3160,10 +3133,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121087290</v>
+        <v>121087313</v>
       </c>
       <c r="B23" t="n">
-        <v>90705</v>
+        <v>79683</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3176,21 +3149,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3200,10 +3173,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541818</v>
+        <v>542053</v>
       </c>
       <c r="R23" t="n">
-        <v>7208201</v>
+        <v>7208323</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3235,7 +3208,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3245,7 +3218,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3272,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121086341</v>
+        <v>121087315</v>
       </c>
       <c r="B24" t="n">
-        <v>90683</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3288,40 +3261,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541777</v>
+        <v>542012</v>
       </c>
       <c r="R24" t="n">
-        <v>7207940</v>
+        <v>7208299</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3350,7 +3325,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3360,12 +3335,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3374,54 +3344,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121087320</v>
+        <v>121086334</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3434,37 +3378,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541956</v>
+        <v>542045</v>
       </c>
       <c r="R25" t="n">
-        <v>7208191</v>
+        <v>7208314</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3493,7 +3445,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3503,7 +3455,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,26 +3471,46 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121086335</v>
+        <v>121087311</v>
       </c>
       <c r="B26" t="n">
-        <v>57348</v>
+        <v>91041</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3542,49 +3519,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541999</v>
+        <v>542016</v>
       </c>
       <c r="R26" t="n">
-        <v>7208264</v>
+        <v>7208338</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3613,7 +3582,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3623,12 +3592,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>S. brevispora s.str</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,38 +3611,38 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121086330</v>
+        <v>121086341</v>
       </c>
       <c r="B27" t="n">
-        <v>57348</v>
+        <v>90693</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3686,31 +3655,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3718,10 +3682,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541697</v>
+        <v>541777</v>
       </c>
       <c r="R27" t="n">
-        <v>7208101</v>
+        <v>7207940</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3753,7 +3717,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3763,12 +3727,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3777,6 +3741,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3795,9 +3760,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3815,10 +3785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121086342</v>
+        <v>121087356</v>
       </c>
       <c r="B28" t="n">
-        <v>90683</v>
+        <v>82385</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3831,40 +3801,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542017</v>
+        <v>541832</v>
       </c>
       <c r="R28" t="n">
-        <v>7208282</v>
+        <v>7207849</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3893,7 +3860,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3903,12 +3870,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3917,54 +3879,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121087333</v>
+        <v>121087341</v>
       </c>
       <c r="B29" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3977,21 +3913,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4001,10 +3937,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541811</v>
+        <v>541840</v>
       </c>
       <c r="R29" t="n">
-        <v>7208014</v>
+        <v>7207901</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4036,7 +3972,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4046,7 +3982,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4073,10 +4009,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121087309</v>
+        <v>121087290</v>
       </c>
       <c r="B30" t="n">
-        <v>90973</v>
+        <v>90715</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4089,21 +4025,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4113,10 +4049,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542016</v>
+        <v>541818</v>
       </c>
       <c r="R30" t="n">
-        <v>7208333</v>
+        <v>7208201</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4148,7 +4084,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4158,7 +4094,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4185,10 +4121,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121087282</v>
+        <v>121087318</v>
       </c>
       <c r="B31" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4201,34 +4137,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541693</v>
+        <v>541944</v>
       </c>
       <c r="R31" t="n">
-        <v>7208064</v>
+        <v>7208213</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4260,7 +4201,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4270,7 +4211,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4297,10 +4238,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121087326</v>
+        <v>121087344</v>
       </c>
       <c r="B32" t="n">
-        <v>90705</v>
+        <v>77538</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4313,21 +4254,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4337,10 +4278,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541877</v>
+        <v>541846</v>
       </c>
       <c r="R32" t="n">
-        <v>7208115</v>
+        <v>7207904</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4372,7 +4313,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4382,7 +4323,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4409,10 +4350,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121087324</v>
+        <v>121087282</v>
       </c>
       <c r="B33" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4425,39 +4366,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541881</v>
+        <v>541693</v>
       </c>
       <c r="R33" t="n">
-        <v>7208125</v>
+        <v>7208064</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4489,7 +4425,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4499,7 +4435,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4526,10 +4462,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121087277</v>
+        <v>121087294</v>
       </c>
       <c r="B34" t="n">
-        <v>97025</v>
+        <v>90711</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4538,25 +4474,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4566,10 +4502,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541725</v>
+        <v>541831</v>
       </c>
       <c r="R34" t="n">
-        <v>7208037</v>
+        <v>7208244</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4601,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4611,7 +4547,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4638,10 +4574,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121087275</v>
+        <v>121087278</v>
       </c>
       <c r="B35" t="n">
-        <v>57348</v>
+        <v>97041</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4650,43 +4586,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541756</v>
+        <v>541725</v>
       </c>
       <c r="R35" t="n">
-        <v>7208000</v>
+        <v>7208037</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4718,7 +4649,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4728,7 +4659,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4755,10 +4686,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121087346</v>
+        <v>121087321</v>
       </c>
       <c r="B36" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4800,10 +4731,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541837</v>
+        <v>541931</v>
       </c>
       <c r="R36" t="n">
-        <v>7207939</v>
+        <v>7208201</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4835,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4845,7 +4776,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4872,10 +4803,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121087286</v>
+        <v>121087502</v>
       </c>
       <c r="B37" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4906,24 +4837,27 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541670</v>
+        <v>541613</v>
       </c>
       <c r="R37" t="n">
-        <v>7208095</v>
+        <v>7208020</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4952,7 +4886,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4962,7 +4896,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4977,22 +4911,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121087313</v>
+        <v>121087333</v>
       </c>
       <c r="B38" t="n">
-        <v>79680</v>
+        <v>90715</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5005,21 +4939,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5029,10 +4963,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542053</v>
+        <v>541811</v>
       </c>
       <c r="R38" t="n">
-        <v>7208323</v>
+        <v>7208014</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5064,7 +4998,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5074,7 +5008,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5101,10 +5035,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121087285</v>
+        <v>121086342</v>
       </c>
       <c r="B39" t="n">
-        <v>57348</v>
+        <v>90693</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5117,42 +5051,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541686</v>
+        <v>542017</v>
       </c>
       <c r="R39" t="n">
-        <v>7208061</v>
+        <v>7208282</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5181,7 +5113,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5191,7 +5123,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5200,28 +5137,54 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121087345</v>
+        <v>121087319</v>
       </c>
       <c r="B40" t="n">
-        <v>74705</v>
+        <v>57351</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,34 +5197,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541847</v>
+        <v>541952</v>
       </c>
       <c r="R40" t="n">
-        <v>7207903</v>
+        <v>7208197</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5293,7 +5261,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5303,7 +5271,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5330,10 +5298,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121087357</v>
+        <v>121087331</v>
       </c>
       <c r="B41" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5346,34 +5314,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541832</v>
+        <v>541817</v>
       </c>
       <c r="R41" t="n">
-        <v>7207849</v>
+        <v>7208035</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5405,7 +5378,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5415,7 +5388,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,10 +5415,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121087312</v>
+        <v>121087350</v>
       </c>
       <c r="B42" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5475,14 +5448,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5491,10 +5460,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542080</v>
+        <v>541839</v>
       </c>
       <c r="R42" t="n">
-        <v>7208265</v>
+        <v>7207908</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5526,7 +5495,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5536,7 +5505,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5563,10 +5532,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121086343</v>
+        <v>121087353</v>
       </c>
       <c r="B43" t="n">
-        <v>90683</v>
+        <v>57351</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5579,40 +5548,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541969</v>
+        <v>541829</v>
       </c>
       <c r="R43" t="n">
-        <v>7208261</v>
+        <v>7207857</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5641,7 +5612,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5651,12 +5622,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5665,54 +5631,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121087351</v>
+        <v>121087291</v>
       </c>
       <c r="B44" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5754,10 +5694,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541838</v>
+        <v>541832</v>
       </c>
       <c r="R44" t="n">
-        <v>7207903</v>
+        <v>7208226</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5789,7 +5729,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5799,7 +5739,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5826,10 +5766,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121087342</v>
+        <v>121087275</v>
       </c>
       <c r="B45" t="n">
-        <v>79708</v>
+        <v>57351</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5838,38 +5778,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541840</v>
+        <v>541756</v>
       </c>
       <c r="R45" t="n">
-        <v>7207901</v>
+        <v>7208000</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5901,7 +5846,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5911,7 +5856,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5938,10 +5883,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121087341</v>
+        <v>121087342</v>
       </c>
       <c r="B46" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5950,25 +5895,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6050,10 +5995,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121087317</v>
+        <v>121087279</v>
       </c>
       <c r="B47" t="n">
-        <v>78598</v>
+        <v>78683</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6066,21 +6011,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6090,10 +6035,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541984</v>
+        <v>541703</v>
       </c>
       <c r="R47" t="n">
-        <v>7208289</v>
+        <v>7208051</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6125,7 +6070,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6135,7 +6080,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6162,10 +6107,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121087332</v>
+        <v>121087317</v>
       </c>
       <c r="B48" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6202,10 +6147,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541817</v>
+        <v>541984</v>
       </c>
       <c r="R48" t="n">
-        <v>7208031</v>
+        <v>7208289</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6237,7 +6182,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6247,7 +6192,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6274,10 +6219,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121087280</v>
+        <v>121087328</v>
       </c>
       <c r="B49" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6290,34 +6235,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541704</v>
+        <v>541831</v>
       </c>
       <c r="R49" t="n">
-        <v>7208050</v>
+        <v>7208060</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6349,7 +6299,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6359,7 +6309,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6386,10 +6336,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121087340</v>
+        <v>121087324</v>
       </c>
       <c r="B50" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6402,34 +6352,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541843</v>
+        <v>541881</v>
       </c>
       <c r="R50" t="n">
-        <v>7207891</v>
+        <v>7208125</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6461,7 +6416,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6471,7 +6426,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6498,10 +6453,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121087283</v>
+        <v>121087314</v>
       </c>
       <c r="B51" t="n">
-        <v>90683</v>
+        <v>78601</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6514,21 +6469,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6538,10 +6493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541684</v>
+        <v>542055</v>
       </c>
       <c r="R51" t="n">
-        <v>7208053</v>
+        <v>7208322</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6573,7 +6528,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6583,7 +6538,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6610,10 +6565,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121087284</v>
+        <v>121087354</v>
       </c>
       <c r="B52" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6626,34 +6581,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541684</v>
+        <v>541832</v>
       </c>
       <c r="R52" t="n">
-        <v>7208052</v>
+        <v>7207855</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6685,7 +6645,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6695,7 +6655,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6722,10 +6682,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121087288</v>
+        <v>121087334</v>
       </c>
       <c r="B53" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6758,7 +6718,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6767,10 +6727,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541752</v>
+        <v>541801</v>
       </c>
       <c r="R53" t="n">
-        <v>7208173</v>
+        <v>7208005</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6802,7 +6762,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6812,7 +6772,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6839,10 +6799,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121087331</v>
+        <v>121087295</v>
       </c>
       <c r="B54" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6855,39 +6815,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541817</v>
+        <v>541831</v>
       </c>
       <c r="R54" t="n">
-        <v>7208035</v>
+        <v>7208244</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6919,7 +6874,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6929,7 +6884,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6956,10 +6911,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121086334</v>
+        <v>121087277</v>
       </c>
       <c r="B55" t="n">
-        <v>57348</v>
+        <v>97035</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6968,49 +6923,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>542045</v>
+        <v>541725</v>
       </c>
       <c r="R55" t="n">
-        <v>7208314</v>
+        <v>7208037</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7039,7 +6986,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7049,12 +6996,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7065,46 +7007,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121087293</v>
+        <v>121086330</v>
       </c>
       <c r="B56" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7135,24 +7057,27 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541831</v>
+        <v>541697</v>
       </c>
       <c r="R56" t="n">
-        <v>7208244</v>
+        <v>7208101</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7181,7 +7106,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7191,7 +7116,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7202,26 +7132,46 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121087350</v>
+        <v>121087357</v>
       </c>
       <c r="B57" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7234,39 +7184,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541839</v>
+        <v>541832</v>
       </c>
       <c r="R57" t="n">
-        <v>7207908</v>
+        <v>7207849</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7298,7 +7243,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7308,7 +7253,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7335,10 +7280,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121087353</v>
+        <v>121087337</v>
       </c>
       <c r="B58" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7351,39 +7296,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541829</v>
+        <v>541811</v>
       </c>
       <c r="R58" t="n">
-        <v>7207857</v>
+        <v>7208016</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7415,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7425,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7452,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121087291</v>
+        <v>121087284</v>
       </c>
       <c r="B59" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7468,39 +7408,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541832</v>
+        <v>541684</v>
       </c>
       <c r="R59" t="n">
-        <v>7208226</v>
+        <v>7208052</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7532,7 +7467,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7542,7 +7477,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7569,10 +7504,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121087287</v>
+        <v>121087335</v>
       </c>
       <c r="B60" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7605,7 +7540,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7614,10 +7549,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541743</v>
+        <v>541794</v>
       </c>
       <c r="R60" t="n">
-        <v>7208173</v>
+        <v>7208008</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7649,7 +7584,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7659,7 +7594,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7686,10 +7621,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121087295</v>
+        <v>121087285</v>
       </c>
       <c r="B61" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7702,34 +7637,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541831</v>
+        <v>541686</v>
       </c>
       <c r="R61" t="n">
-        <v>7208244</v>
+        <v>7208061</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7761,7 +7701,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7771,7 +7711,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7798,10 +7738,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121087321</v>
+        <v>121087276</v>
       </c>
       <c r="B62" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7834,7 +7774,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7843,10 +7783,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541931</v>
+        <v>541745</v>
       </c>
       <c r="R62" t="n">
-        <v>7208201</v>
+        <v>7207997</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7878,7 +7818,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7888,7 +7828,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7915,10 +7855,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121086331</v>
+        <v>121087343</v>
       </c>
       <c r="B63" t="n">
-        <v>57348</v>
+        <v>82385</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7931,45 +7871,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541703</v>
+        <v>541847</v>
       </c>
       <c r="R63" t="n">
-        <v>7208142</v>
+        <v>7207905</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7998,7 +7930,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8008,12 +7940,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8024,46 +7951,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121087334</v>
+        <v>121087323</v>
       </c>
       <c r="B64" t="n">
-        <v>57348</v>
+        <v>57367</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8076,16 +7983,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8096,7 +8003,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8105,10 +8012,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541801</v>
+        <v>541897</v>
       </c>
       <c r="R64" t="n">
-        <v>7208005</v>
+        <v>7208135</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8140,7 +8047,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8150,7 +8057,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8177,10 +8084,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121087316</v>
+        <v>121087281</v>
       </c>
       <c r="B65" t="n">
-        <v>90683</v>
+        <v>74708</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8193,21 +8100,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8217,10 +8124,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541984</v>
+        <v>541693</v>
       </c>
       <c r="R65" t="n">
-        <v>7208289</v>
+        <v>7208064</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8252,7 +8159,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8262,7 +8169,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8289,10 +8196,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121087322</v>
+        <v>121087332</v>
       </c>
       <c r="B66" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8329,10 +8236,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541931</v>
+        <v>541817</v>
       </c>
       <c r="R66" t="n">
-        <v>7208192</v>
+        <v>7208031</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8364,7 +8271,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8374,7 +8281,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8401,10 +8308,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121087348</v>
+        <v>121086335</v>
       </c>
       <c r="B67" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8435,24 +8342,27 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541837</v>
+        <v>541999</v>
       </c>
       <c r="R67" t="n">
-        <v>7207922</v>
+        <v>7208264</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8481,7 +8391,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8491,7 +8401,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8502,26 +8417,41 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121087319</v>
+        <v>121087237</v>
       </c>
       <c r="B68" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8552,24 +8482,27 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541952</v>
+        <v>542031</v>
       </c>
       <c r="R68" t="n">
-        <v>7208197</v>
+        <v>7208267</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8598,7 +8531,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8608,7 +8541,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8623,22 +8556,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121087502</v>
+        <v>121087340</v>
       </c>
       <c r="B69" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8651,45 +8584,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541613</v>
+        <v>541843</v>
       </c>
       <c r="R69" t="n">
-        <v>7208020</v>
+        <v>7207891</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8718,7 +8643,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8728,7 +8653,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8743,22 +8668,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121087344</v>
+        <v>121086336</v>
       </c>
       <c r="B70" t="n">
-        <v>77535</v>
+        <v>57351</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8771,37 +8696,45 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541846</v>
+        <v>541937</v>
       </c>
       <c r="R70" t="n">
-        <v>7207904</v>
+        <v>7208222</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8830,7 +8763,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8840,7 +8773,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8851,26 +8789,46 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121087279</v>
+        <v>121087283</v>
       </c>
       <c r="B71" t="n">
-        <v>78680</v>
+        <v>90693</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8883,21 +8841,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8907,10 +8865,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541703</v>
+        <v>541684</v>
       </c>
       <c r="R71" t="n">
-        <v>7208051</v>
+        <v>7208053</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8942,7 +8900,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8952,7 +8910,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8979,10 +8937,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121087352</v>
+        <v>121086331</v>
       </c>
       <c r="B72" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8995,37 +8953,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541827</v>
+        <v>541703</v>
       </c>
       <c r="R72" t="n">
-        <v>7207856</v>
+        <v>7208142</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9054,7 +9020,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9064,7 +9030,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9075,26 +9046,46 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121087294</v>
+        <v>121087327</v>
       </c>
       <c r="B73" t="n">
-        <v>90701</v>
+        <v>57504</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9107,34 +9098,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541831</v>
+        <v>541871</v>
       </c>
       <c r="R73" t="n">
-        <v>7208244</v>
+        <v>7208138</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9166,7 +9161,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9176,7 +9171,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9203,10 +9198,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121087314</v>
+        <v>121087293</v>
       </c>
       <c r="B74" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9219,34 +9214,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>542055</v>
+        <v>541831</v>
       </c>
       <c r="R74" t="n">
-        <v>7208322</v>
+        <v>7208244</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9315,10 +9315,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121087328</v>
+        <v>121087288</v>
       </c>
       <c r="B75" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541831</v>
+        <v>541752</v>
       </c>
       <c r="R75" t="n">
-        <v>7208060</v>
+        <v>7208173</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9432,10 +9432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121087276</v>
+        <v>121087336</v>
       </c>
       <c r="B76" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541745</v>
+        <v>541811</v>
       </c>
       <c r="R76" t="n">
-        <v>7207997</v>
+        <v>7208016</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 40737-2024 artfynd.xlsx
+++ b/artfynd/A 40737-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087352</v>
+        <v>121087349</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541827</v>
+        <v>541836</v>
       </c>
       <c r="R3" t="n">
-        <v>7207856</v>
+        <v>7207921</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087349</v>
+        <v>121087348</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -935,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541836</v>
+        <v>541837</v>
       </c>
       <c r="R4" t="n">
-        <v>7207921</v>
+        <v>7207922</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121087348</v>
+        <v>121086337</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1050,24 +1055,27 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541837</v>
+        <v>541917</v>
       </c>
       <c r="R5" t="n">
-        <v>7207922</v>
+        <v>7208182</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,26 +1130,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121086337</v>
+        <v>121087352</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,45 +1177,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541917</v>
+        <v>541827</v>
       </c>
       <c r="R6" t="n">
-        <v>7208182</v>
+        <v>7207856</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,12 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,31 +1257,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -3507,10 +3507,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121087311</v>
+        <v>121087341</v>
       </c>
       <c r="B26" t="n">
-        <v>91041</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3519,25 +3519,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542016</v>
+        <v>541840</v>
       </c>
       <c r="R26" t="n">
-        <v>7208338</v>
+        <v>7207901</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3592,12 +3592,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>S. brevispora s.str</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3608,21 +3603,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3639,10 +3619,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121086341</v>
+        <v>121087290</v>
       </c>
       <c r="B27" t="n">
-        <v>90693</v>
+        <v>90715</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3655,40 +3635,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541777</v>
+        <v>541818</v>
       </c>
       <c r="R27" t="n">
-        <v>7207940</v>
+        <v>7208201</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3717,7 +3694,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3727,12 +3704,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3741,54 +3713,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121087356</v>
+        <v>121087311</v>
       </c>
       <c r="B28" t="n">
-        <v>82385</v>
+        <v>91041</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3797,25 +3743,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3825,10 +3771,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541832</v>
+        <v>542016</v>
       </c>
       <c r="R28" t="n">
-        <v>7207849</v>
+        <v>7208338</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3860,7 +3806,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3870,7 +3816,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>S. brevispora s.str</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3881,6 +3832,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3897,10 +3863,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121087341</v>
+        <v>121086341</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3913,37 +3879,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541840</v>
+        <v>541777</v>
       </c>
       <c r="R29" t="n">
-        <v>7207901</v>
+        <v>7207940</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3972,7 +3941,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3982,7 +3951,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3991,28 +3965,54 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121087290</v>
+        <v>121087356</v>
       </c>
       <c r="B30" t="n">
-        <v>90715</v>
+        <v>82385</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4049,10 +4049,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541818</v>
+        <v>541832</v>
       </c>
       <c r="R30" t="n">
-        <v>7208201</v>
+        <v>7207849</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4121,10 +4121,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121087318</v>
+        <v>121087344</v>
       </c>
       <c r="B31" t="n">
-        <v>57351</v>
+        <v>77538</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4137,39 +4137,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541944</v>
+        <v>541846</v>
       </c>
       <c r="R31" t="n">
-        <v>7208213</v>
+        <v>7207904</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4201,7 +4196,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4211,7 +4206,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4238,10 +4233,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121087344</v>
+        <v>121087318</v>
       </c>
       <c r="B32" t="n">
-        <v>77538</v>
+        <v>57351</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4254,34 +4249,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541846</v>
+        <v>541944</v>
       </c>
       <c r="R32" t="n">
-        <v>7207904</v>
+        <v>7208213</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5649,10 +5649,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121087291</v>
+        <v>121087342</v>
       </c>
       <c r="B44" t="n">
-        <v>57351</v>
+        <v>79711</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5661,43 +5661,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541832</v>
+        <v>541840</v>
       </c>
       <c r="R44" t="n">
-        <v>7208226</v>
+        <v>7207901</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5729,7 +5724,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5739,7 +5734,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5766,7 +5761,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121087275</v>
+        <v>121087291</v>
       </c>
       <c r="B45" t="n">
         <v>57351</v>
@@ -5811,10 +5806,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541756</v>
+        <v>541832</v>
       </c>
       <c r="R45" t="n">
-        <v>7208000</v>
+        <v>7208226</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5846,7 +5841,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5856,7 +5851,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5883,10 +5878,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121087342</v>
+        <v>121087275</v>
       </c>
       <c r="B46" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5895,38 +5890,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541840</v>
+        <v>541756</v>
       </c>
       <c r="R46" t="n">
-        <v>7207901</v>
+        <v>7208000</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 40737-2024 artfynd.xlsx
+++ b/artfynd/A 40737-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087349</v>
+        <v>121087352</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541836</v>
+        <v>541827</v>
       </c>
       <c r="R3" t="n">
-        <v>7207921</v>
+        <v>7207856</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087348</v>
+        <v>121087349</v>
       </c>
       <c r="B4" t="n">
         <v>57351</v>
@@ -940,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541837</v>
+        <v>541836</v>
       </c>
       <c r="R4" t="n">
-        <v>7207922</v>
+        <v>7207921</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121086337</v>
+        <v>121087348</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1055,27 +1050,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541917</v>
+        <v>541837</v>
       </c>
       <c r="R5" t="n">
-        <v>7208182</v>
+        <v>7207922</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,41 +1117,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087352</v>
+        <v>121086337</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,37 +1149,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541827</v>
+        <v>541917</v>
       </c>
       <c r="R6" t="n">
-        <v>7207856</v>
+        <v>7208182</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1226,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,26 +1242,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087351</v>
+        <v>121087326</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,39 +1289,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541838</v>
+        <v>541877</v>
       </c>
       <c r="R7" t="n">
-        <v>7207903</v>
+        <v>7208115</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1353,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121087286</v>
+        <v>121087351</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1426,7 +1421,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1435,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541670</v>
+        <v>541838</v>
       </c>
       <c r="R8" t="n">
-        <v>7208095</v>
+        <v>7207903</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1475,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121086343</v>
+        <v>121087286</v>
       </c>
       <c r="B9" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,40 +1518,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541969</v>
+        <v>541670</v>
       </c>
       <c r="R9" t="n">
-        <v>7208261</v>
+        <v>7208095</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,12 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,54 +1601,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087310</v>
+        <v>121086343</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
+        <v>90693</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,37 +1635,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542016</v>
+        <v>541969</v>
       </c>
       <c r="R10" t="n">
-        <v>7208334</v>
+        <v>7208261</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1728,7 +1697,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1738,7 +1707,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,28 +1721,54 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087326</v>
+        <v>121087310</v>
       </c>
       <c r="B11" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541877</v>
+        <v>542016</v>
       </c>
       <c r="R11" t="n">
-        <v>7208115</v>
+        <v>7208334</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121087314</v>
+        <v>121087354</v>
       </c>
       <c r="B51" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6469,34 +6469,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>542055</v>
+        <v>541832</v>
       </c>
       <c r="R51" t="n">
-        <v>7208322</v>
+        <v>7207855</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6528,7 +6533,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6538,7 +6543,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6565,7 +6570,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121087354</v>
+        <v>121087334</v>
       </c>
       <c r="B52" t="n">
         <v>57351</v>
@@ -6610,10 +6615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541832</v>
+        <v>541801</v>
       </c>
       <c r="R52" t="n">
-        <v>7207855</v>
+        <v>7208005</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6645,7 +6650,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6655,7 +6660,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6682,10 +6687,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121087334</v>
+        <v>121087314</v>
       </c>
       <c r="B53" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6698,39 +6703,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541801</v>
+        <v>542055</v>
       </c>
       <c r="R53" t="n">
-        <v>7208005</v>
+        <v>7208322</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6799,10 +6799,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121087295</v>
+        <v>121087277</v>
       </c>
       <c r="B54" t="n">
-        <v>90697</v>
+        <v>97035</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6811,25 +6811,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541831</v>
+        <v>541725</v>
       </c>
       <c r="R54" t="n">
-        <v>7208244</v>
+        <v>7208037</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6911,10 +6911,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121087277</v>
+        <v>121087295</v>
       </c>
       <c r="B55" t="n">
-        <v>97035</v>
+        <v>90697</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6923,25 +6923,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541725</v>
+        <v>541831</v>
       </c>
       <c r="R55" t="n">
-        <v>7208037</v>
+        <v>7208244</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7392,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121087284</v>
+        <v>121087343</v>
       </c>
       <c r="B59" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7408,21 +7408,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541684</v>
+        <v>541847</v>
       </c>
       <c r="R59" t="n">
-        <v>7208052</v>
+        <v>7207905</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7504,10 +7504,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121087335</v>
+        <v>121087323</v>
       </c>
       <c r="B60" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7520,16 +7520,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541794</v>
+        <v>541897</v>
       </c>
       <c r="R60" t="n">
-        <v>7208008</v>
+        <v>7208135</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7621,10 +7621,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121087285</v>
+        <v>121087284</v>
       </c>
       <c r="B61" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7637,39 +7637,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541686</v>
+        <v>541684</v>
       </c>
       <c r="R61" t="n">
-        <v>7208061</v>
+        <v>7208052</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7701,7 +7696,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7711,7 +7706,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7738,7 +7733,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121087276</v>
+        <v>121087335</v>
       </c>
       <c r="B62" t="n">
         <v>57351</v>
@@ -7783,10 +7778,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541745</v>
+        <v>541794</v>
       </c>
       <c r="R62" t="n">
-        <v>7207997</v>
+        <v>7208008</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7818,7 +7813,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7828,7 +7823,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7855,10 +7850,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121087343</v>
+        <v>121087285</v>
       </c>
       <c r="B63" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7871,34 +7866,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541847</v>
+        <v>541686</v>
       </c>
       <c r="R63" t="n">
-        <v>7207905</v>
+        <v>7208061</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7967,10 +7967,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121087323</v>
+        <v>121087276</v>
       </c>
       <c r="B64" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7983,16 +7983,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541897</v>
+        <v>541745</v>
       </c>
       <c r="R64" t="n">
-        <v>7208135</v>
+        <v>7207997</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 40737-2024 artfynd.xlsx
+++ b/artfynd/A 40737-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087322</v>
+        <v>121087333</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541931</v>
+        <v>541811</v>
       </c>
       <c r="R2" t="n">
-        <v>7208192</v>
+        <v>7208014</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087352</v>
+        <v>121087326</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541827</v>
+        <v>541877</v>
       </c>
       <c r="R3" t="n">
-        <v>7207856</v>
+        <v>7208115</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087349</v>
+        <v>121087343</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>82385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541836</v>
+        <v>541847</v>
       </c>
       <c r="R4" t="n">
-        <v>7207921</v>
+        <v>7207905</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121087348</v>
+        <v>121087356</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>82385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541837</v>
+        <v>541832</v>
       </c>
       <c r="R5" t="n">
-        <v>7207922</v>
+        <v>7207849</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121086337</v>
+        <v>121087337</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,45 +1139,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541917</v>
+        <v>541811</v>
       </c>
       <c r="R6" t="n">
-        <v>7208182</v>
+        <v>7208016</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,12 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,41 +1219,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087326</v>
+        <v>121087284</v>
       </c>
       <c r="B7" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541877</v>
+        <v>541684</v>
       </c>
       <c r="R7" t="n">
-        <v>7208115</v>
+        <v>7208052</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1348,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121087351</v>
+        <v>121086337</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1419,24 +1381,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541838</v>
+        <v>541917</v>
       </c>
       <c r="R8" t="n">
-        <v>7207903</v>
+        <v>7208182</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,7 +1440,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,23 +1456,38 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087286</v>
+        <v>121087276</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1538,7 +1523,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1547,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541670</v>
+        <v>541745</v>
       </c>
       <c r="R9" t="n">
-        <v>7208095</v>
+        <v>7207997</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1582,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121086343</v>
+        <v>121087355</v>
       </c>
       <c r="B10" t="n">
-        <v>90693</v>
+        <v>77942</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,44 +1616,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541969</v>
+        <v>541834</v>
       </c>
       <c r="R10" t="n">
-        <v>7208261</v>
+        <v>7207850</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1697,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,12 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,54 +1698,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087310</v>
+        <v>121086342</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>90693</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,37 +1732,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542016</v>
+        <v>542017</v>
       </c>
       <c r="R11" t="n">
-        <v>7208334</v>
+        <v>7208282</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1840,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1850,7 +1804,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,28 +1818,54 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121087320</v>
+        <v>121087345</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,21 +1878,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1917,10 +1902,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541956</v>
+        <v>541847</v>
       </c>
       <c r="R12" t="n">
-        <v>7208191</v>
+        <v>7207903</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1952,7 +1937,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1962,7 +1947,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121087355</v>
+        <v>121087352</v>
       </c>
       <c r="B13" t="n">
-        <v>77942</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2001,25 +1986,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2029,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541834</v>
+        <v>541827</v>
       </c>
       <c r="R13" t="n">
-        <v>7207850</v>
+        <v>7207856</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2064,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2074,7 +2059,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121087280</v>
+        <v>121087350</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,34 +2102,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541704</v>
+        <v>541839</v>
       </c>
       <c r="R14" t="n">
-        <v>7208050</v>
+        <v>7207908</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2176,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2186,7 +2176,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,7 +2203,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121087339</v>
+        <v>121087321</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2258,10 +2248,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541843</v>
+        <v>541931</v>
       </c>
       <c r="R15" t="n">
-        <v>7207891</v>
+        <v>7208201</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2293,7 +2283,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,7 +2293,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2330,10 +2320,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121087346</v>
+        <v>121087342</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>79711</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,43 +2332,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541837</v>
+        <v>541840</v>
       </c>
       <c r="R16" t="n">
-        <v>7207939</v>
+        <v>7207901</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2410,7 +2395,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,7 +2405,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2447,10 +2432,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121087287</v>
+        <v>121086341</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>90693</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,42 +2448,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541743</v>
+        <v>541777</v>
       </c>
       <c r="R17" t="n">
-        <v>7208173</v>
+        <v>7207940</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2527,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2537,7 +2520,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,28 +2534,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087309</v>
+        <v>121087287</v>
       </c>
       <c r="B18" t="n">
-        <v>90983</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,34 +2594,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542016</v>
+        <v>541743</v>
       </c>
       <c r="R18" t="n">
-        <v>7208333</v>
+        <v>7208173</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2639,7 +2658,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2649,7 +2668,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,10 +2695,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087316</v>
+        <v>121087502</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2692,37 +2711,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541984</v>
+        <v>541613</v>
       </c>
       <c r="R19" t="n">
-        <v>7208289</v>
+        <v>7208020</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2751,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2761,7 +2788,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,22 +2803,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121087345</v>
+        <v>121087313</v>
       </c>
       <c r="B20" t="n">
-        <v>74708</v>
+        <v>79683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,21 +2831,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2828,10 +2855,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541847</v>
+        <v>542053</v>
       </c>
       <c r="R20" t="n">
-        <v>7207903</v>
+        <v>7208323</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2863,7 +2890,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2873,7 +2900,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,10 +2927,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087312</v>
+        <v>121087340</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2916,43 +2943,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542080</v>
+        <v>541843</v>
       </c>
       <c r="R21" t="n">
-        <v>7208265</v>
+        <v>7207891</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2984,7 +3002,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2994,7 +3012,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087329</v>
+        <v>121087332</v>
       </c>
       <c r="B22" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3037,21 +3055,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3061,10 +3079,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541819</v>
+        <v>541817</v>
       </c>
       <c r="R22" t="n">
-        <v>7208041</v>
+        <v>7208031</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3096,7 +3114,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3106,7 +3124,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3133,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121087313</v>
+        <v>121086343</v>
       </c>
       <c r="B23" t="n">
-        <v>79683</v>
+        <v>90693</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3149,37 +3167,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542053</v>
+        <v>541969</v>
       </c>
       <c r="R23" t="n">
-        <v>7208323</v>
+        <v>7208261</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3208,7 +3229,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3218,7 +3239,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,28 +3253,54 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121087315</v>
+        <v>121087322</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3261,39 +3313,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542012</v>
+        <v>541931</v>
       </c>
       <c r="R24" t="n">
-        <v>7208299</v>
+        <v>7208192</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3325,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3335,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3362,10 +3409,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121086334</v>
+        <v>121087282</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3378,45 +3425,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542045</v>
+        <v>541693</v>
       </c>
       <c r="R25" t="n">
-        <v>7208314</v>
+        <v>7208064</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3445,7 +3484,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3455,12 +3494,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3471,46 +3505,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121087341</v>
+        <v>121087279</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>78683</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3523,21 +3537,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3547,10 +3561,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541840</v>
+        <v>541703</v>
       </c>
       <c r="R26" t="n">
-        <v>7207901</v>
+        <v>7208051</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3582,7 +3596,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3592,7 +3606,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3619,10 +3633,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121087290</v>
+        <v>121087310</v>
       </c>
       <c r="B27" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3635,21 +3649,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3659,10 +3673,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541818</v>
+        <v>542016</v>
       </c>
       <c r="R27" t="n">
-        <v>7208201</v>
+        <v>7208334</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3694,7 +3708,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3704,7 +3718,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3731,10 +3745,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121087311</v>
+        <v>121087293</v>
       </c>
       <c r="B28" t="n">
-        <v>91041</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3743,38 +3757,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542016</v>
+        <v>541831</v>
       </c>
       <c r="R28" t="n">
-        <v>7208338</v>
+        <v>7208244</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3806,7 +3825,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3816,12 +3835,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>S. brevispora s.str</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,21 +3846,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3863,10 +3862,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121086341</v>
+        <v>121087288</v>
       </c>
       <c r="B29" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3879,40 +3878,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541777</v>
+        <v>541752</v>
       </c>
       <c r="R29" t="n">
-        <v>7207940</v>
+        <v>7208173</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3941,7 +3942,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3951,12 +3952,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3965,54 +3961,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121087356</v>
+        <v>121087334</v>
       </c>
       <c r="B30" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4025,34 +3995,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541832</v>
+        <v>541801</v>
       </c>
       <c r="R30" t="n">
-        <v>7207849</v>
+        <v>7208005</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4084,7 +4059,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4094,7 +4069,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4121,10 +4096,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121087344</v>
+        <v>121087353</v>
       </c>
       <c r="B31" t="n">
-        <v>77538</v>
+        <v>57351</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4137,34 +4112,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541846</v>
+        <v>541829</v>
       </c>
       <c r="R31" t="n">
-        <v>7207904</v>
+        <v>7207857</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4196,7 +4176,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4206,7 +4186,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4233,7 +4213,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121087318</v>
+        <v>121087336</v>
       </c>
       <c r="B32" t="n">
         <v>57351</v>
@@ -4278,10 +4258,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541944</v>
+        <v>541811</v>
       </c>
       <c r="R32" t="n">
-        <v>7208213</v>
+        <v>7208016</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4313,7 +4293,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4323,7 +4303,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4350,10 +4330,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121087282</v>
+        <v>121087327</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4366,34 +4346,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541693</v>
+        <v>541871</v>
       </c>
       <c r="R33" t="n">
-        <v>7208064</v>
+        <v>7208138</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4425,7 +4409,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4435,7 +4419,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4462,10 +4446,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121087294</v>
+        <v>121087309</v>
       </c>
       <c r="B34" t="n">
-        <v>90711</v>
+        <v>90983</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4478,21 +4462,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4502,10 +4486,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541831</v>
+        <v>542016</v>
       </c>
       <c r="R34" t="n">
-        <v>7208244</v>
+        <v>7208333</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4537,7 +4521,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4547,7 +4531,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4574,10 +4558,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121087278</v>
+        <v>121087311</v>
       </c>
       <c r="B35" t="n">
-        <v>97041</v>
+        <v>91041</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4586,25 +4570,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>2062</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4614,10 +4598,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541725</v>
+        <v>542016</v>
       </c>
       <c r="R35" t="n">
-        <v>7208037</v>
+        <v>7208338</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4649,7 +4633,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4659,7 +4643,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>S. brevispora s.str</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4670,6 +4659,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4686,7 +4690,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121087321</v>
+        <v>121087348</v>
       </c>
       <c r="B36" t="n">
         <v>57351</v>
@@ -4722,7 +4726,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4731,10 +4735,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541931</v>
+        <v>541837</v>
       </c>
       <c r="R36" t="n">
-        <v>7208201</v>
+        <v>7207922</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4766,7 +4770,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,7 +4780,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4803,7 +4807,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121087502</v>
+        <v>121087354</v>
       </c>
       <c r="B37" t="n">
         <v>57351</v>
@@ -4837,27 +4841,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541613</v>
+        <v>541832</v>
       </c>
       <c r="R37" t="n">
-        <v>7208020</v>
+        <v>7207855</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4886,7 +4887,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4896,7 +4897,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4911,22 +4912,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121087333</v>
+        <v>121087316</v>
       </c>
       <c r="B38" t="n">
-        <v>90715</v>
+        <v>90693</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4939,21 +4940,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4963,10 +4964,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541811</v>
+        <v>541984</v>
       </c>
       <c r="R38" t="n">
-        <v>7208014</v>
+        <v>7208289</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4998,7 +4999,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5008,7 +5009,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5035,10 +5036,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121086342</v>
+        <v>121087341</v>
       </c>
       <c r="B39" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5051,40 +5052,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542017</v>
+        <v>541840</v>
       </c>
       <c r="R39" t="n">
-        <v>7208282</v>
+        <v>7207901</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5113,7 +5111,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5123,12 +5121,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5137,51 +5130,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121087319</v>
+        <v>121086335</v>
       </c>
       <c r="B40" t="n">
         <v>57351</v>
@@ -5215,24 +5182,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541952</v>
+        <v>541999</v>
       </c>
       <c r="R40" t="n">
-        <v>7208197</v>
+        <v>7208264</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5261,7 +5231,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5271,7 +5241,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5282,23 +5257,38 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121087331</v>
+        <v>121087346</v>
       </c>
       <c r="B41" t="n">
         <v>57351</v>
@@ -5334,7 +5324,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5343,10 +5333,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541817</v>
+        <v>541837</v>
       </c>
       <c r="R41" t="n">
-        <v>7208035</v>
+        <v>7207939</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5378,7 +5368,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5388,7 +5378,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5415,7 +5405,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121087350</v>
+        <v>121087286</v>
       </c>
       <c r="B42" t="n">
         <v>57351</v>
@@ -5451,7 +5441,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5460,10 +5450,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541839</v>
+        <v>541670</v>
       </c>
       <c r="R42" t="n">
-        <v>7207908</v>
+        <v>7208095</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5495,7 +5485,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5505,7 +5495,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5532,7 +5522,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121087353</v>
+        <v>121087237</v>
       </c>
       <c r="B43" t="n">
         <v>57351</v>
@@ -5566,24 +5556,27 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541829</v>
+        <v>542031</v>
       </c>
       <c r="R43" t="n">
-        <v>7207857</v>
+        <v>7208267</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5612,7 +5605,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5622,7 +5615,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5637,22 +5630,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121087342</v>
+        <v>121087318</v>
       </c>
       <c r="B44" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5661,38 +5654,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541840</v>
+        <v>541944</v>
       </c>
       <c r="R44" t="n">
-        <v>7207901</v>
+        <v>7208213</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5724,7 +5722,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5734,7 +5732,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5761,7 +5759,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121087291</v>
+        <v>121087351</v>
       </c>
       <c r="B45" t="n">
         <v>57351</v>
@@ -5806,10 +5804,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541832</v>
+        <v>541838</v>
       </c>
       <c r="R45" t="n">
-        <v>7208226</v>
+        <v>7207903</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5841,7 +5839,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5851,7 +5849,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5878,7 +5876,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121087275</v>
+        <v>121087335</v>
       </c>
       <c r="B46" t="n">
         <v>57351</v>
@@ -5923,10 +5921,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541756</v>
+        <v>541794</v>
       </c>
       <c r="R46" t="n">
-        <v>7208000</v>
+        <v>7208008</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5958,7 +5956,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5968,7 +5966,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5995,10 +5993,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121087279</v>
+        <v>121086330</v>
       </c>
       <c r="B47" t="n">
-        <v>78683</v>
+        <v>57351</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6011,37 +6009,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541703</v>
+        <v>541697</v>
       </c>
       <c r="R47" t="n">
-        <v>7208051</v>
+        <v>7208101</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6070,7 +6076,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6080,7 +6086,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6091,26 +6102,46 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121087317</v>
+        <v>121087344</v>
       </c>
       <c r="B48" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6123,21 +6154,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6147,10 +6178,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541984</v>
+        <v>541846</v>
       </c>
       <c r="R48" t="n">
-        <v>7208289</v>
+        <v>7207904</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6182,7 +6213,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6192,7 +6223,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6219,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121087328</v>
+        <v>121087281</v>
       </c>
       <c r="B49" t="n">
-        <v>57351</v>
+        <v>74708</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6235,39 +6266,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541831</v>
+        <v>541693</v>
       </c>
       <c r="R49" t="n">
-        <v>7208060</v>
+        <v>7208064</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6299,7 +6325,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6309,7 +6335,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6336,10 +6362,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121087324</v>
+        <v>121087278</v>
       </c>
       <c r="B50" t="n">
-        <v>57351</v>
+        <v>97041</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6348,43 +6374,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541881</v>
+        <v>541725</v>
       </c>
       <c r="R50" t="n">
-        <v>7208125</v>
+        <v>7208037</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6416,7 +6437,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6426,7 +6447,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6453,7 +6474,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121087354</v>
+        <v>121087339</v>
       </c>
       <c r="B51" t="n">
         <v>57351</v>
@@ -6498,10 +6519,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541832</v>
+        <v>541843</v>
       </c>
       <c r="R51" t="n">
-        <v>7207855</v>
+        <v>7207891</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6533,7 +6554,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6543,7 +6564,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6570,7 +6591,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121087334</v>
+        <v>121087349</v>
       </c>
       <c r="B52" t="n">
         <v>57351</v>
@@ -6615,10 +6636,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541801</v>
+        <v>541836</v>
       </c>
       <c r="R52" t="n">
-        <v>7208005</v>
+        <v>7207921</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6650,7 +6671,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6660,7 +6681,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6687,10 +6708,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121087314</v>
+        <v>121087291</v>
       </c>
       <c r="B53" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6703,34 +6724,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542055</v>
+        <v>541832</v>
       </c>
       <c r="R53" t="n">
-        <v>7208322</v>
+        <v>7208226</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6762,7 +6788,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6772,7 +6798,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6799,10 +6825,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121087277</v>
+        <v>121087323</v>
       </c>
       <c r="B54" t="n">
-        <v>97035</v>
+        <v>57367</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6811,38 +6837,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541725</v>
+        <v>541897</v>
       </c>
       <c r="R54" t="n">
-        <v>7208037</v>
+        <v>7208135</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6874,7 +6905,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6884,7 +6915,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6911,10 +6942,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121087295</v>
+        <v>121087294</v>
       </c>
       <c r="B55" t="n">
-        <v>90697</v>
+        <v>90711</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6927,21 +6958,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7023,10 +7054,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121086330</v>
+        <v>121087329</v>
       </c>
       <c r="B56" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7039,45 +7070,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541697</v>
+        <v>541819</v>
       </c>
       <c r="R56" t="n">
-        <v>7208101</v>
+        <v>7208041</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7106,7 +7129,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7116,12 +7139,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7132,46 +7150,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121087357</v>
+        <v>121087328</v>
       </c>
       <c r="B57" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7184,34 +7182,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541832</v>
+        <v>541831</v>
       </c>
       <c r="R57" t="n">
-        <v>7207849</v>
+        <v>7208060</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7243,7 +7246,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7253,7 +7256,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7280,10 +7283,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121087337</v>
+        <v>121087331</v>
       </c>
       <c r="B58" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7296,34 +7299,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541811</v>
+        <v>541817</v>
       </c>
       <c r="R58" t="n">
-        <v>7208016</v>
+        <v>7208035</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7355,7 +7363,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7373,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,10 +7400,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121087343</v>
+        <v>121087320</v>
       </c>
       <c r="B59" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7408,21 +7416,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7432,10 +7440,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541847</v>
+        <v>541956</v>
       </c>
       <c r="R59" t="n">
-        <v>7207905</v>
+        <v>7208191</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7467,7 +7475,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7477,7 +7485,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7504,10 +7512,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121087323</v>
+        <v>121086336</v>
       </c>
       <c r="B60" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7520,16 +7528,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7538,24 +7546,27 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541897</v>
+        <v>541937</v>
       </c>
       <c r="R60" t="n">
-        <v>7208135</v>
+        <v>7208222</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7584,7 +7595,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7594,7 +7605,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7605,26 +7621,46 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121087284</v>
+        <v>121087319</v>
       </c>
       <c r="B61" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7637,34 +7673,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541684</v>
+        <v>541952</v>
       </c>
       <c r="R61" t="n">
-        <v>7208052</v>
+        <v>7208197</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7696,7 +7737,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7706,7 +7747,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7733,7 +7774,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121087335</v>
+        <v>121086334</v>
       </c>
       <c r="B62" t="n">
         <v>57351</v>
@@ -7767,24 +7808,27 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541794</v>
+        <v>542045</v>
       </c>
       <c r="R62" t="n">
-        <v>7208008</v>
+        <v>7208314</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7813,7 +7857,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7823,7 +7867,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7834,23 +7883,43 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121087285</v>
+        <v>121087312</v>
       </c>
       <c r="B63" t="n">
         <v>57351</v>
@@ -7883,10 +7952,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7895,10 +7968,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541686</v>
+        <v>542080</v>
       </c>
       <c r="R63" t="n">
-        <v>7208061</v>
+        <v>7208265</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7930,7 +8003,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7940,7 +8013,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7967,10 +8040,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121087276</v>
+        <v>121087283</v>
       </c>
       <c r="B64" t="n">
-        <v>57351</v>
+        <v>90693</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7983,39 +8056,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541745</v>
+        <v>541684</v>
       </c>
       <c r="R64" t="n">
-        <v>7207997</v>
+        <v>7208053</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8047,7 +8115,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8057,7 +8125,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8084,10 +8152,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121087281</v>
+        <v>121086331</v>
       </c>
       <c r="B65" t="n">
-        <v>74708</v>
+        <v>57351</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8100,37 +8168,45 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541693</v>
+        <v>541703</v>
       </c>
       <c r="R65" t="n">
-        <v>7208064</v>
+        <v>7208142</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8159,7 +8235,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8169,7 +8245,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8180,26 +8261,46 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121087332</v>
+        <v>121087285</v>
       </c>
       <c r="B66" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8212,34 +8313,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541817</v>
+        <v>541686</v>
       </c>
       <c r="R66" t="n">
-        <v>7208031</v>
+        <v>7208061</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8271,7 +8377,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8281,7 +8387,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8308,10 +8414,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121086335</v>
+        <v>121087295</v>
       </c>
       <c r="B67" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8324,45 +8430,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541999</v>
+        <v>541831</v>
       </c>
       <c r="R67" t="n">
-        <v>7208264</v>
+        <v>7208244</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8391,7 +8489,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8401,12 +8499,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8417,41 +8510,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121087237</v>
+        <v>121087357</v>
       </c>
       <c r="B68" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8464,45 +8542,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>542031</v>
+        <v>541832</v>
       </c>
       <c r="R68" t="n">
-        <v>7208267</v>
+        <v>7207849</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8531,7 +8601,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8541,7 +8611,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8556,19 +8626,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121087340</v>
+        <v>121087317</v>
       </c>
       <c r="B69" t="n">
         <v>78601</v>
@@ -8608,10 +8678,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541843</v>
+        <v>541984</v>
       </c>
       <c r="R69" t="n">
-        <v>7207891</v>
+        <v>7208289</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8643,7 +8713,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8653,7 +8723,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8680,10 +8750,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121086336</v>
+        <v>121087280</v>
       </c>
       <c r="B70" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8696,45 +8766,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541937</v>
+        <v>541704</v>
       </c>
       <c r="R70" t="n">
-        <v>7208222</v>
+        <v>7208050</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8763,7 +8825,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8773,12 +8835,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8789,46 +8846,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121087283</v>
+        <v>121087290</v>
       </c>
       <c r="B71" t="n">
-        <v>90693</v>
+        <v>90715</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8841,21 +8878,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8865,10 +8902,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541684</v>
+        <v>541818</v>
       </c>
       <c r="R71" t="n">
-        <v>7208053</v>
+        <v>7208201</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8900,7 +8937,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8910,7 +8947,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8937,10 +8974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121086331</v>
+        <v>121087277</v>
       </c>
       <c r="B72" t="n">
-        <v>57351</v>
+        <v>97035</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8949,49 +8986,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541703</v>
+        <v>541725</v>
       </c>
       <c r="R72" t="n">
-        <v>7208142</v>
+        <v>7208037</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9020,7 +9049,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9030,12 +9059,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9046,46 +9070,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121087327</v>
+        <v>121087314</v>
       </c>
       <c r="B73" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9098,38 +9102,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541871</v>
+        <v>542055</v>
       </c>
       <c r="R73" t="n">
-        <v>7208138</v>
+        <v>7208322</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9198,7 +9198,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121087293</v>
+        <v>121087315</v>
       </c>
       <c r="B74" t="n">
         <v>57351</v>
@@ -9243,10 +9243,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541831</v>
+        <v>542012</v>
       </c>
       <c r="R74" t="n">
-        <v>7208244</v>
+        <v>7208299</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9315,7 +9315,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121087288</v>
+        <v>121087324</v>
       </c>
       <c r="B75" t="n">
         <v>57351</v>
@@ -9360,10 +9360,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541752</v>
+        <v>541881</v>
       </c>
       <c r="R75" t="n">
-        <v>7208173</v>
+        <v>7208125</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9432,7 +9432,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121087336</v>
+        <v>121087275</v>
       </c>
       <c r="B76" t="n">
         <v>57351</v>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541811</v>
+        <v>541756</v>
       </c>
       <c r="R76" t="n">
-        <v>7208016</v>
+        <v>7208000</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 40737-2024 artfynd.xlsx
+++ b/artfynd/A 40737-2024 artfynd.xlsx
@@ -2320,10 +2320,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121087342</v>
+        <v>121086341</v>
       </c>
       <c r="B16" t="n">
-        <v>79711</v>
+        <v>90693</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2332,41 +2332,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541840</v>
+        <v>541777</v>
       </c>
       <c r="R16" t="n">
-        <v>7207901</v>
+        <v>7207940</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2395,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2405,7 +2408,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,28 +2422,54 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121086341</v>
+        <v>121087287</v>
       </c>
       <c r="B17" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2448,40 +2482,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541777</v>
+        <v>541743</v>
       </c>
       <c r="R17" t="n">
-        <v>7207940</v>
+        <v>7208173</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2510,7 +2546,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,12 +2556,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2534,51 +2565,25 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087287</v>
+        <v>121087502</v>
       </c>
       <c r="B18" t="n">
         <v>57351</v>
@@ -2612,24 +2617,27 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541743</v>
+        <v>541613</v>
       </c>
       <c r="R18" t="n">
-        <v>7208173</v>
+        <v>7208020</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2658,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2668,7 +2676,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,22 +2691,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087502</v>
+        <v>121087342</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>79711</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2707,49 +2715,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541613</v>
+        <v>541840</v>
       </c>
       <c r="R19" t="n">
-        <v>7208020</v>
+        <v>7207901</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2803,12 +2803,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121087318</v>
+        <v>121087278</v>
       </c>
       <c r="B44" t="n">
-        <v>57351</v>
+        <v>97041</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5654,43 +5654,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541944</v>
+        <v>541725</v>
       </c>
       <c r="R44" t="n">
-        <v>7208213</v>
+        <v>7208037</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5722,7 +5717,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5732,7 +5727,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5759,10 +5754,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121087351</v>
+        <v>121087344</v>
       </c>
       <c r="B45" t="n">
-        <v>57351</v>
+        <v>77538</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5775,39 +5770,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541838</v>
+        <v>541846</v>
       </c>
       <c r="R45" t="n">
-        <v>7207903</v>
+        <v>7207904</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5839,7 +5829,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5849,7 +5839,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5876,10 +5866,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121087335</v>
+        <v>121087281</v>
       </c>
       <c r="B46" t="n">
-        <v>57351</v>
+        <v>74708</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5892,39 +5882,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541794</v>
+        <v>541693</v>
       </c>
       <c r="R46" t="n">
-        <v>7208008</v>
+        <v>7208064</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5956,7 +5941,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5966,7 +5951,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5993,7 +5978,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121086330</v>
+        <v>121087318</v>
       </c>
       <c r="B47" t="n">
         <v>57351</v>
@@ -6027,27 +6012,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541697</v>
+        <v>541944</v>
       </c>
       <c r="R47" t="n">
-        <v>7208101</v>
+        <v>7208213</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6076,7 +6058,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6086,12 +6068,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6102,46 +6079,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121087344</v>
+        <v>121087351</v>
       </c>
       <c r="B48" t="n">
-        <v>77538</v>
+        <v>57351</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6154,34 +6111,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541846</v>
+        <v>541838</v>
       </c>
       <c r="R48" t="n">
-        <v>7207904</v>
+        <v>7207903</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6213,7 +6175,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6223,7 +6185,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6250,10 +6212,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121087281</v>
+        <v>121087335</v>
       </c>
       <c r="B49" t="n">
-        <v>74708</v>
+        <v>57351</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6266,34 +6228,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541693</v>
+        <v>541794</v>
       </c>
       <c r="R49" t="n">
-        <v>7208064</v>
+        <v>7208008</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6325,7 +6292,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6335,7 +6302,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6362,10 +6329,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121087278</v>
+        <v>121086330</v>
       </c>
       <c r="B50" t="n">
-        <v>97041</v>
+        <v>57351</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6374,41 +6341,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541725</v>
+        <v>541697</v>
       </c>
       <c r="R50" t="n">
-        <v>7208037</v>
+        <v>7208101</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6437,7 +6412,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6447,7 +6422,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6458,16 +6438,36 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121087294</v>
+        <v>121087329</v>
       </c>
       <c r="B55" t="n">
-        <v>90711</v>
+        <v>90697</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6958,21 +6958,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541831</v>
+        <v>541819</v>
       </c>
       <c r="R55" t="n">
-        <v>7208244</v>
+        <v>7208041</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7054,10 +7054,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121087329</v>
+        <v>121087294</v>
       </c>
       <c r="B56" t="n">
-        <v>90697</v>
+        <v>90711</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7070,21 +7070,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7094,10 +7094,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541819</v>
+        <v>541831</v>
       </c>
       <c r="R56" t="n">
-        <v>7208041</v>
+        <v>7208244</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7400,10 +7400,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121087320</v>
+        <v>121087283</v>
       </c>
       <c r="B59" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7416,21 +7416,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541956</v>
+        <v>541684</v>
       </c>
       <c r="R59" t="n">
-        <v>7208191</v>
+        <v>7208053</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7512,10 +7512,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121086336</v>
+        <v>121087320</v>
       </c>
       <c r="B60" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7528,45 +7528,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541937</v>
+        <v>541956</v>
       </c>
       <c r="R60" t="n">
-        <v>7208222</v>
+        <v>7208191</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7595,7 +7587,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7605,12 +7597,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7621,43 +7608,23 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121087319</v>
+        <v>121086336</v>
       </c>
       <c r="B61" t="n">
         <v>57351</v>
@@ -7691,24 +7658,27 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541952</v>
+        <v>541937</v>
       </c>
       <c r="R61" t="n">
-        <v>7208197</v>
+        <v>7208222</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7737,7 +7707,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7747,7 +7717,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7758,23 +7733,43 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121086334</v>
+        <v>121087319</v>
       </c>
       <c r="B62" t="n">
         <v>57351</v>
@@ -7808,27 +7803,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>542045</v>
+        <v>541952</v>
       </c>
       <c r="R62" t="n">
-        <v>7208314</v>
+        <v>7208197</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7857,7 +7849,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7867,12 +7859,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7883,43 +7870,23 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121087312</v>
+        <v>121086334</v>
       </c>
       <c r="B63" t="n">
         <v>57351</v>
@@ -7952,29 +7919,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542080</v>
+        <v>542045</v>
       </c>
       <c r="R63" t="n">
-        <v>7208265</v>
+        <v>7208314</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8003,7 +7969,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8013,7 +7979,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8024,26 +7995,46 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121087283</v>
+        <v>121087312</v>
       </c>
       <c r="B64" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8056,34 +8047,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541684</v>
+        <v>542080</v>
       </c>
       <c r="R64" t="n">
-        <v>7208053</v>
+        <v>7208265</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8750,10 +8750,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121087280</v>
+        <v>121087277</v>
       </c>
       <c r="B70" t="n">
-        <v>78601</v>
+        <v>97035</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8762,25 +8762,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541704</v>
+        <v>541725</v>
       </c>
       <c r="R70" t="n">
-        <v>7208050</v>
+        <v>7208037</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8862,10 +8862,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121087290</v>
+        <v>121087280</v>
       </c>
       <c r="B71" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541818</v>
+        <v>541704</v>
       </c>
       <c r="R71" t="n">
-        <v>7208201</v>
+        <v>7208050</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8974,10 +8974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121087277</v>
+        <v>121087290</v>
       </c>
       <c r="B72" t="n">
-        <v>97035</v>
+        <v>90715</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8986,25 +8986,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9014,10 +9014,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541725</v>
+        <v>541818</v>
       </c>
       <c r="R72" t="n">
-        <v>7208037</v>
+        <v>7208201</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 40737-2024 artfynd.xlsx
+++ b/artfynd/A 40737-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087333</v>
+        <v>121086343</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>90705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541811</v>
+        <v>541969</v>
       </c>
       <c r="R2" t="n">
-        <v>7208014</v>
+        <v>7208261</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +777,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087326</v>
+        <v>121087280</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +837,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541877</v>
+        <v>541704</v>
       </c>
       <c r="R3" t="n">
-        <v>7208115</v>
+        <v>7208050</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +906,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087343</v>
+        <v>121087321</v>
       </c>
       <c r="B4" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +949,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541847</v>
+        <v>541931</v>
       </c>
       <c r="R4" t="n">
-        <v>7207905</v>
+        <v>7208201</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121087356</v>
+        <v>121087318</v>
       </c>
       <c r="B5" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1066,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541832</v>
+        <v>541944</v>
       </c>
       <c r="R5" t="n">
-        <v>7207849</v>
+        <v>7208213</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087337</v>
+        <v>121087313</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1183,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541811</v>
+        <v>542053</v>
       </c>
       <c r="R6" t="n">
-        <v>7208016</v>
+        <v>7208323</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087284</v>
+        <v>121087355</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>77945</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1291,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541684</v>
+        <v>541834</v>
       </c>
       <c r="R7" t="n">
-        <v>7208052</v>
+        <v>7207850</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121086337</v>
+        <v>121087342</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>79714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,49 +1403,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541917</v>
+        <v>541840</v>
       </c>
       <c r="R8" t="n">
-        <v>7208182</v>
+        <v>7207901</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,12 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,38 +1487,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087276</v>
+        <v>121087293</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1532,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541745</v>
+        <v>541831</v>
       </c>
       <c r="R9" t="n">
-        <v>7207997</v>
+        <v>7208244</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1567,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087355</v>
+        <v>121087324</v>
       </c>
       <c r="B10" t="n">
-        <v>77942</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,38 +1632,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>498</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541834</v>
+        <v>541881</v>
       </c>
       <c r="R10" t="n">
-        <v>7207850</v>
+        <v>7208125</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1710,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121086342</v>
+        <v>121087285</v>
       </c>
       <c r="B11" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,40 +1753,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542017</v>
+        <v>541686</v>
       </c>
       <c r="R11" t="n">
-        <v>7208282</v>
+        <v>7208061</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,12 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,54 +1836,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121087345</v>
+        <v>121087316</v>
       </c>
       <c r="B12" t="n">
-        <v>74708</v>
+        <v>90705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,21 +1870,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1902,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541847</v>
+        <v>541984</v>
       </c>
       <c r="R12" t="n">
-        <v>7207903</v>
+        <v>7208289</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1937,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121087352</v>
+        <v>121087317</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2014,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541827</v>
+        <v>541984</v>
       </c>
       <c r="R13" t="n">
-        <v>7207856</v>
+        <v>7208289</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2049,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +2051,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121087350</v>
+        <v>121087282</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2102,39 +2094,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541839</v>
+        <v>541693</v>
       </c>
       <c r="R14" t="n">
-        <v>7207908</v>
+        <v>7208064</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2166,7 +2153,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,7 +2163,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,7 +2190,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121087321</v>
+        <v>121087346</v>
       </c>
       <c r="B15" t="n">
         <v>57351</v>
@@ -2248,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541931</v>
+        <v>541837</v>
       </c>
       <c r="R15" t="n">
-        <v>7208201</v>
+        <v>7207939</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2283,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2293,7 +2280,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2320,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121086341</v>
+        <v>121087311</v>
       </c>
       <c r="B16" t="n">
-        <v>90693</v>
+        <v>91053</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2332,44 +2319,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541777</v>
+        <v>542016</v>
       </c>
       <c r="R16" t="n">
-        <v>7207940</v>
+        <v>7208338</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2398,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,12 +2392,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på granstubbe</t>
+          <t>S. brevispora s.str</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,54 +2406,43 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>ullticka</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121087287</v>
+        <v>121087310</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,39 +2455,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541743</v>
+        <v>542016</v>
       </c>
       <c r="R17" t="n">
-        <v>7208173</v>
+        <v>7208334</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2546,7 +2514,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2556,7 +2524,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2583,10 +2551,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087502</v>
+        <v>121086341</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>90705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2599,45 +2567,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541613</v>
+        <v>541777</v>
       </c>
       <c r="R18" t="n">
-        <v>7208020</v>
+        <v>7207940</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2666,7 +2629,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,7 +2639,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,28 +2653,54 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087342</v>
+        <v>121087277</v>
       </c>
       <c r="B19" t="n">
-        <v>79711</v>
+        <v>97048</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2719,21 +2713,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2743,10 +2737,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541840</v>
+        <v>541725</v>
       </c>
       <c r="R19" t="n">
-        <v>7207901</v>
+        <v>7208037</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2778,7 +2772,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,7 +2782,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2815,10 +2809,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121087313</v>
+        <v>121087328</v>
       </c>
       <c r="B20" t="n">
-        <v>79683</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2831,34 +2825,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542053</v>
+        <v>541831</v>
       </c>
       <c r="R20" t="n">
-        <v>7208323</v>
+        <v>7208060</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2890,7 +2889,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2900,7 +2899,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2927,10 +2926,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087340</v>
+        <v>121087294</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>90723</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,21 +2942,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2967,10 +2966,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541843</v>
+        <v>541831</v>
       </c>
       <c r="R21" t="n">
-        <v>7207891</v>
+        <v>7208244</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3002,7 +3001,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3012,7 +3011,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3038,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087332</v>
+        <v>121087343</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3055,21 +3054,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3079,10 +3078,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541817</v>
+        <v>541847</v>
       </c>
       <c r="R22" t="n">
-        <v>7208031</v>
+        <v>7207905</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3114,7 +3113,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3124,7 +3123,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3151,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121086343</v>
+        <v>121087348</v>
       </c>
       <c r="B23" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3167,40 +3166,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541969</v>
+        <v>541837</v>
       </c>
       <c r="R23" t="n">
-        <v>7208261</v>
+        <v>7207922</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3229,7 +3230,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3239,12 +3240,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3253,54 +3249,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121087322</v>
+        <v>121087237</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3313,37 +3283,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541931</v>
+        <v>542031</v>
       </c>
       <c r="R24" t="n">
-        <v>7208192</v>
+        <v>7208267</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3372,7 +3350,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3360,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,22 +3375,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121087282</v>
+        <v>121087278</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>97054</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3421,25 +3399,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3449,10 +3427,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541693</v>
+        <v>541725</v>
       </c>
       <c r="R25" t="n">
-        <v>7208064</v>
+        <v>7208037</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3484,7 +3462,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3494,7 +3472,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3521,10 +3499,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121087279</v>
+        <v>121087284</v>
       </c>
       <c r="B26" t="n">
-        <v>78683</v>
+        <v>78604</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3537,21 +3515,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3561,10 +3539,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541703</v>
+        <v>541684</v>
       </c>
       <c r="R26" t="n">
-        <v>7208051</v>
+        <v>7208052</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3596,7 +3574,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3606,7 +3584,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3633,10 +3611,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121087310</v>
+        <v>121086342</v>
       </c>
       <c r="B27" t="n">
-        <v>90697</v>
+        <v>90705</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3649,37 +3627,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542016</v>
+        <v>542017</v>
       </c>
       <c r="R27" t="n">
-        <v>7208334</v>
+        <v>7208282</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3708,7 +3689,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3718,7 +3699,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3727,25 +3713,51 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121087293</v>
+        <v>121086336</v>
       </c>
       <c r="B28" t="n">
         <v>57351</v>
@@ -3779,24 +3791,27 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541831</v>
+        <v>541937</v>
       </c>
       <c r="R28" t="n">
-        <v>7208244</v>
+        <v>7208222</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3825,7 +3840,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3835,7 +3850,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3846,23 +3866,43 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121087288</v>
+        <v>121087287</v>
       </c>
       <c r="B29" t="n">
         <v>57351</v>
@@ -3898,7 +3938,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3907,7 +3947,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541752</v>
+        <v>541743</v>
       </c>
       <c r="R29" t="n">
         <v>7208173</v>
@@ -3942,7 +3982,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3952,7 +3992,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3979,10 +4019,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121087334</v>
+        <v>121087279</v>
       </c>
       <c r="B30" t="n">
-        <v>57351</v>
+        <v>78686</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,39 +4035,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541801</v>
+        <v>541703</v>
       </c>
       <c r="R30" t="n">
-        <v>7208005</v>
+        <v>7208051</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4059,7 +4094,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4069,7 +4104,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4096,7 +4131,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121087353</v>
+        <v>121087288</v>
       </c>
       <c r="B31" t="n">
         <v>57351</v>
@@ -4132,7 +4167,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4141,10 +4176,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541829</v>
+        <v>541752</v>
       </c>
       <c r="R31" t="n">
-        <v>7207857</v>
+        <v>7208173</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4176,7 +4211,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4186,7 +4221,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4213,7 +4248,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121087336</v>
+        <v>121086331</v>
       </c>
       <c r="B32" t="n">
         <v>57351</v>
@@ -4247,24 +4282,27 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541811</v>
+        <v>541703</v>
       </c>
       <c r="R32" t="n">
-        <v>7208016</v>
+        <v>7208142</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4293,7 +4331,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4303,7 +4341,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4314,26 +4357,46 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121087327</v>
+        <v>121087281</v>
       </c>
       <c r="B33" t="n">
-        <v>57504</v>
+        <v>74710</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4346,38 +4409,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541871</v>
+        <v>541693</v>
       </c>
       <c r="R33" t="n">
-        <v>7208138</v>
+        <v>7208064</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4409,7 +4468,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4419,7 +4478,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4446,10 +4505,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121087309</v>
+        <v>121087329</v>
       </c>
       <c r="B34" t="n">
-        <v>90983</v>
+        <v>90709</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4462,21 +4521,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4486,10 +4545,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542016</v>
+        <v>541819</v>
       </c>
       <c r="R34" t="n">
-        <v>7208333</v>
+        <v>7208041</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4521,7 +4580,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4531,7 +4590,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4558,10 +4617,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121087311</v>
+        <v>121087290</v>
       </c>
       <c r="B35" t="n">
-        <v>91041</v>
+        <v>90727</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,25 +4629,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4598,10 +4657,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542016</v>
+        <v>541818</v>
       </c>
       <c r="R35" t="n">
-        <v>7208338</v>
+        <v>7208201</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4633,7 +4692,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4643,12 +4702,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>S. brevispora s.str</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,21 +4713,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4690,7 +4729,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121087348</v>
+        <v>121087351</v>
       </c>
       <c r="B36" t="n">
         <v>57351</v>
@@ -4735,10 +4774,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541837</v>
+        <v>541838</v>
       </c>
       <c r="R36" t="n">
-        <v>7207922</v>
+        <v>7207903</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4770,7 +4809,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4780,7 +4819,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4924,10 +4963,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121087316</v>
+        <v>121087502</v>
       </c>
       <c r="B38" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4940,37 +4979,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541984</v>
+        <v>541613</v>
       </c>
       <c r="R38" t="n">
-        <v>7208289</v>
+        <v>7208020</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4999,7 +5046,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +5056,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5024,22 +5071,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121087341</v>
+        <v>121087283</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5052,21 +5099,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5076,10 +5123,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541840</v>
+        <v>541684</v>
       </c>
       <c r="R39" t="n">
-        <v>7207901</v>
+        <v>7208053</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5111,7 +5158,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5121,7 +5168,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5148,10 +5195,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121086335</v>
+        <v>121087333</v>
       </c>
       <c r="B40" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5164,45 +5211,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541999</v>
+        <v>541811</v>
       </c>
       <c r="R40" t="n">
-        <v>7208264</v>
+        <v>7208014</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5231,7 +5270,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5241,12 +5280,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5257,41 +5291,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121087346</v>
+        <v>121087323</v>
       </c>
       <c r="B41" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5304,16 +5323,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5324,7 +5343,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5333,10 +5352,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541837</v>
+        <v>541897</v>
       </c>
       <c r="R41" t="n">
-        <v>7207939</v>
+        <v>7208135</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5368,7 +5387,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5378,7 +5397,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5405,7 +5424,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121087286</v>
+        <v>121087335</v>
       </c>
       <c r="B42" t="n">
         <v>57351</v>
@@ -5441,7 +5460,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5450,10 +5469,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541670</v>
+        <v>541794</v>
       </c>
       <c r="R42" t="n">
-        <v>7208095</v>
+        <v>7208008</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5485,7 +5504,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5495,7 +5514,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5522,10 +5541,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121087237</v>
+        <v>121087309</v>
       </c>
       <c r="B43" t="n">
-        <v>57351</v>
+        <v>90995</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5538,45 +5557,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542031</v>
+        <v>542016</v>
       </c>
       <c r="R43" t="n">
-        <v>7208267</v>
+        <v>7208333</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5605,7 +5616,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5615,7 +5626,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5630,22 +5641,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121087278</v>
+        <v>121086337</v>
       </c>
       <c r="B44" t="n">
-        <v>97041</v>
+        <v>57351</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5654,41 +5665,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541725</v>
+        <v>541917</v>
       </c>
       <c r="R44" t="n">
-        <v>7208037</v>
+        <v>7208182</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5717,7 +5736,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5727,7 +5746,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5738,26 +5762,41 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121087344</v>
+        <v>121087352</v>
       </c>
       <c r="B45" t="n">
-        <v>77538</v>
+        <v>78604</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5770,21 +5809,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5794,10 +5833,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541846</v>
+        <v>541827</v>
       </c>
       <c r="R45" t="n">
-        <v>7207904</v>
+        <v>7207856</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5829,7 +5868,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5839,7 +5878,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5866,10 +5905,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121087281</v>
+        <v>121087339</v>
       </c>
       <c r="B46" t="n">
-        <v>74708</v>
+        <v>57351</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5882,34 +5921,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541693</v>
+        <v>541843</v>
       </c>
       <c r="R46" t="n">
-        <v>7208064</v>
+        <v>7207891</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5941,7 +5985,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5951,7 +5995,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5978,7 +6022,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121087318</v>
+        <v>121087315</v>
       </c>
       <c r="B47" t="n">
         <v>57351</v>
@@ -6023,10 +6067,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541944</v>
+        <v>542012</v>
       </c>
       <c r="R47" t="n">
-        <v>7208213</v>
+        <v>7208299</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6058,7 +6102,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6068,7 +6112,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6095,10 +6139,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121087351</v>
+        <v>121087337</v>
       </c>
       <c r="B48" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6111,39 +6155,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541838</v>
+        <v>541811</v>
       </c>
       <c r="R48" t="n">
-        <v>7207903</v>
+        <v>7208016</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6175,7 +6214,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6185,7 +6224,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6212,10 +6251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121087335</v>
+        <v>121087332</v>
       </c>
       <c r="B49" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6228,39 +6267,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541794</v>
+        <v>541817</v>
       </c>
       <c r="R49" t="n">
-        <v>7208008</v>
+        <v>7208031</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6292,7 +6326,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6302,7 +6336,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6329,10 +6363,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121086330</v>
+        <v>121087345</v>
       </c>
       <c r="B50" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6345,45 +6379,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541697</v>
+        <v>541847</v>
       </c>
       <c r="R50" t="n">
-        <v>7208101</v>
+        <v>7207903</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6412,7 +6438,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6422,12 +6448,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6438,46 +6459,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121087339</v>
+        <v>121087295</v>
       </c>
       <c r="B51" t="n">
-        <v>57351</v>
+        <v>90709</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6490,39 +6491,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541843</v>
+        <v>541831</v>
       </c>
       <c r="R51" t="n">
-        <v>7207891</v>
+        <v>7208244</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6554,7 +6550,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6564,7 +6560,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6591,10 +6587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121087349</v>
+        <v>121087320</v>
       </c>
       <c r="B52" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6607,39 +6603,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541836</v>
+        <v>541956</v>
       </c>
       <c r="R52" t="n">
-        <v>7207921</v>
+        <v>7208191</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6671,7 +6662,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6681,7 +6672,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6708,7 +6699,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121087291</v>
+        <v>121086334</v>
       </c>
       <c r="B53" t="n">
         <v>57351</v>
@@ -6742,24 +6733,27 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>541832</v>
+        <v>542045</v>
       </c>
       <c r="R53" t="n">
-        <v>7208226</v>
+        <v>7208314</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6788,7 +6782,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6798,7 +6792,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6809,26 +6808,46 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121087323</v>
+        <v>121087314</v>
       </c>
       <c r="B54" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6841,39 +6860,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541897</v>
+        <v>542055</v>
       </c>
       <c r="R54" t="n">
-        <v>7208135</v>
+        <v>7208322</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6905,7 +6919,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6915,7 +6929,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6942,10 +6956,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121087329</v>
+        <v>121087353</v>
       </c>
       <c r="B55" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6958,34 +6972,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541819</v>
+        <v>541829</v>
       </c>
       <c r="R55" t="n">
-        <v>7208041</v>
+        <v>7207857</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7017,7 +7036,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7027,7 +7046,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7054,10 +7073,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121087294</v>
+        <v>121087275</v>
       </c>
       <c r="B56" t="n">
-        <v>90711</v>
+        <v>57351</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7070,34 +7089,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541831</v>
+        <v>541756</v>
       </c>
       <c r="R56" t="n">
-        <v>7208244</v>
+        <v>7208000</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7129,7 +7153,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7139,7 +7163,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7166,10 +7190,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121087328</v>
+        <v>121087327</v>
       </c>
       <c r="B57" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7182,27 +7206,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7211,10 +7234,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541831</v>
+        <v>541871</v>
       </c>
       <c r="R57" t="n">
-        <v>7208060</v>
+        <v>7208138</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7246,7 +7269,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7256,7 +7279,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7283,7 +7306,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121087331</v>
+        <v>121087334</v>
       </c>
       <c r="B58" t="n">
         <v>57351</v>
@@ -7319,7 +7342,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7328,10 +7351,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541817</v>
+        <v>541801</v>
       </c>
       <c r="R58" t="n">
-        <v>7208035</v>
+        <v>7208005</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7363,7 +7386,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7373,7 +7396,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7400,10 +7423,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121087283</v>
+        <v>121087291</v>
       </c>
       <c r="B59" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7416,34 +7439,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541684</v>
+        <v>541832</v>
       </c>
       <c r="R59" t="n">
-        <v>7208053</v>
+        <v>7208226</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7475,7 +7503,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7485,7 +7513,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7512,10 +7540,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121087320</v>
+        <v>121087276</v>
       </c>
       <c r="B60" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7528,34 +7556,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541956</v>
+        <v>541745</v>
       </c>
       <c r="R60" t="n">
-        <v>7208191</v>
+        <v>7207997</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7587,7 +7620,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7597,7 +7630,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7624,10 +7657,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121086336</v>
+        <v>121087344</v>
       </c>
       <c r="B61" t="n">
-        <v>57351</v>
+        <v>77541</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7640,45 +7673,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541937</v>
+        <v>541846</v>
       </c>
       <c r="R61" t="n">
-        <v>7208222</v>
+        <v>7207904</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7707,7 +7732,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7717,12 +7742,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7733,46 +7753,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121087319</v>
+        <v>121087322</v>
       </c>
       <c r="B62" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7785,39 +7785,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541952</v>
+        <v>541931</v>
       </c>
       <c r="R62" t="n">
-        <v>7208197</v>
+        <v>7208192</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7849,7 +7844,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7859,7 +7854,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7886,10 +7881,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121086334</v>
+        <v>121087341</v>
       </c>
       <c r="B63" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7902,45 +7897,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542045</v>
+        <v>541840</v>
       </c>
       <c r="R63" t="n">
-        <v>7208314</v>
+        <v>7207901</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7969,7 +7956,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7979,12 +7966,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7995,46 +7977,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121087312</v>
+        <v>121087340</v>
       </c>
       <c r="B64" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8047,43 +8009,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542080</v>
+        <v>541843</v>
       </c>
       <c r="R64" t="n">
-        <v>7208265</v>
+        <v>7207891</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8115,7 +8068,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8125,7 +8078,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8152,10 +8105,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121086331</v>
+        <v>121087326</v>
       </c>
       <c r="B65" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8168,45 +8121,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541703</v>
+        <v>541877</v>
       </c>
       <c r="R65" t="n">
-        <v>7208142</v>
+        <v>7208115</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8235,7 +8180,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8245,12 +8190,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8261,43 +8201,23 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121087285</v>
+        <v>121087331</v>
       </c>
       <c r="B66" t="n">
         <v>57351</v>
@@ -8333,7 +8253,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8342,10 +8262,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541686</v>
+        <v>541817</v>
       </c>
       <c r="R66" t="n">
-        <v>7208061</v>
+        <v>7208035</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8377,7 +8297,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8387,7 +8307,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8414,10 +8334,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121087295</v>
+        <v>121087350</v>
       </c>
       <c r="B67" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8430,34 +8350,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541831</v>
+        <v>541839</v>
       </c>
       <c r="R67" t="n">
-        <v>7208244</v>
+        <v>7207908</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8489,7 +8414,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8499,7 +8424,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8526,10 +8451,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121087357</v>
+        <v>121087286</v>
       </c>
       <c r="B68" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8542,34 +8467,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541832</v>
+        <v>541670</v>
       </c>
       <c r="R68" t="n">
-        <v>7207849</v>
+        <v>7208095</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8601,7 +8531,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8611,7 +8541,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8638,10 +8568,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121087317</v>
+        <v>121087356</v>
       </c>
       <c r="B69" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8654,21 +8584,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8678,10 +8608,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541984</v>
+        <v>541832</v>
       </c>
       <c r="R69" t="n">
-        <v>7208289</v>
+        <v>7207849</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8713,7 +8643,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8723,7 +8653,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8750,10 +8680,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121087277</v>
+        <v>121087357</v>
       </c>
       <c r="B70" t="n">
-        <v>97035</v>
+        <v>78604</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8762,25 +8692,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8790,10 +8720,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541725</v>
+        <v>541832</v>
       </c>
       <c r="R70" t="n">
-        <v>7208037</v>
+        <v>7207849</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8825,7 +8755,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8835,7 +8765,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8862,10 +8792,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121087280</v>
+        <v>121087312</v>
       </c>
       <c r="B71" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8878,34 +8808,43 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541704</v>
+        <v>542080</v>
       </c>
       <c r="R71" t="n">
-        <v>7208050</v>
+        <v>7208265</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8937,7 +8876,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8947,7 +8886,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8974,10 +8913,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121087290</v>
+        <v>121086330</v>
       </c>
       <c r="B72" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8990,37 +8929,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541818</v>
+        <v>541697</v>
       </c>
       <c r="R72" t="n">
-        <v>7208201</v>
+        <v>7208101</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9049,7 +8996,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9059,7 +9006,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9070,26 +9022,46 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121087314</v>
+        <v>121087349</v>
       </c>
       <c r="B73" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9102,34 +9074,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>542055</v>
+        <v>541836</v>
       </c>
       <c r="R73" t="n">
-        <v>7208322</v>
+        <v>7207921</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9161,7 +9138,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9171,7 +9148,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9198,7 +9175,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121087315</v>
+        <v>121087319</v>
       </c>
       <c r="B74" t="n">
         <v>57351</v>
@@ -9243,10 +9220,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>542012</v>
+        <v>541952</v>
       </c>
       <c r="R74" t="n">
-        <v>7208299</v>
+        <v>7208197</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9278,7 +9255,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9288,7 +9265,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9315,7 +9292,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121087324</v>
+        <v>121086335</v>
       </c>
       <c r="B75" t="n">
         <v>57351</v>
@@ -9349,24 +9326,27 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541881</v>
+        <v>541999</v>
       </c>
       <c r="R75" t="n">
-        <v>7208125</v>
+        <v>7208264</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9395,7 +9375,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9405,7 +9385,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9416,23 +9401,38 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121087275</v>
+        <v>121087336</v>
       </c>
       <c r="B76" t="n">
         <v>57351</v>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541756</v>
+        <v>541811</v>
       </c>
       <c r="R76" t="n">
-        <v>7208000</v>
+        <v>7208016</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 40737-2024 artfynd.xlsx
+++ b/artfynd/A 40737-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121086343</v>
+        <v>121087328</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541969</v>
+        <v>541831</v>
       </c>
       <c r="R2" t="n">
-        <v>7208261</v>
+        <v>7208060</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,54 +774,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087280</v>
+        <v>121087309</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>90996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541704</v>
+        <v>542016</v>
       </c>
       <c r="R3" t="n">
-        <v>7208050</v>
+        <v>7208333</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -896,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087321</v>
+        <v>121087295</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541931</v>
+        <v>541831</v>
       </c>
       <c r="R4" t="n">
-        <v>7208201</v>
+        <v>7208244</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121087318</v>
+        <v>121087345</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541944</v>
+        <v>541847</v>
       </c>
       <c r="R5" t="n">
-        <v>7208213</v>
+        <v>7207903</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087313</v>
+        <v>121087288</v>
       </c>
       <c r="B6" t="n">
-        <v>79686</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542053</v>
+        <v>541752</v>
       </c>
       <c r="R6" t="n">
-        <v>7208323</v>
+        <v>7208173</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1242,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087355</v>
+        <v>121087329</v>
       </c>
       <c r="B7" t="n">
-        <v>77945</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>498</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1319,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541834</v>
+        <v>541819</v>
       </c>
       <c r="R7" t="n">
-        <v>7207850</v>
+        <v>7208041</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1354,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121087342</v>
+        <v>121087349</v>
       </c>
       <c r="B8" t="n">
-        <v>79714</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,38 +1369,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541840</v>
+        <v>541836</v>
       </c>
       <c r="R8" t="n">
-        <v>7207901</v>
+        <v>7207921</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,7 +1474,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087293</v>
+        <v>121087348</v>
       </c>
       <c r="B9" t="n">
         <v>57351</v>
@@ -1548,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541831</v>
+        <v>541837</v>
       </c>
       <c r="R9" t="n">
-        <v>7208244</v>
+        <v>7207922</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1583,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087324</v>
+        <v>121087350</v>
       </c>
       <c r="B10" t="n">
         <v>57351</v>
@@ -1665,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541881</v>
+        <v>541839</v>
       </c>
       <c r="R10" t="n">
-        <v>7208125</v>
+        <v>7207908</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1700,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,7 +1708,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087285</v>
+        <v>121086334</v>
       </c>
       <c r="B11" t="n">
         <v>57351</v>
@@ -1771,24 +1742,27 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541686</v>
+        <v>542045</v>
       </c>
       <c r="R11" t="n">
-        <v>7208061</v>
+        <v>7208314</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1817,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1801,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,26 +1817,46 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121087316</v>
+        <v>121086343</v>
       </c>
       <c r="B12" t="n">
-        <v>90705</v>
+        <v>90706</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1888,19 +1887,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541984</v>
+        <v>541969</v>
       </c>
       <c r="R12" t="n">
-        <v>7208289</v>
+        <v>7208261</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1941,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,28 +1955,54 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121087317</v>
+        <v>121087316</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>90706</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,21 +2015,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2078,7 +2111,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121087282</v>
+        <v>121087341</v>
       </c>
       <c r="B14" t="n">
         <v>78604</v>
@@ -2118,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541693</v>
+        <v>541840</v>
       </c>
       <c r="R14" t="n">
-        <v>7208064</v>
+        <v>7207901</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2153,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2163,7 +2196,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,10 +2223,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121087346</v>
+        <v>121087332</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,39 +2239,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541837</v>
+        <v>541817</v>
       </c>
       <c r="R15" t="n">
-        <v>7207939</v>
+        <v>7208031</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2270,7 +2298,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2308,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2335,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121087311</v>
+        <v>121087354</v>
       </c>
       <c r="B16" t="n">
-        <v>91053</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,38 +2347,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542016</v>
+        <v>541832</v>
       </c>
       <c r="R16" t="n">
-        <v>7208338</v>
+        <v>7207855</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2382,7 +2415,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,12 +2425,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>S. brevispora s.str</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,21 +2436,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ullticka</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2439,10 +2452,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121087310</v>
+        <v>121087286</v>
       </c>
       <c r="B17" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2455,34 +2468,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542016</v>
+        <v>541670</v>
       </c>
       <c r="R17" t="n">
-        <v>7208334</v>
+        <v>7208095</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2514,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2524,7 +2542,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2551,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121086341</v>
+        <v>121087315</v>
       </c>
       <c r="B18" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,40 +2585,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541777</v>
+        <v>542012</v>
       </c>
       <c r="R18" t="n">
-        <v>7207940</v>
+        <v>7208299</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2629,7 +2649,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2639,12 +2659,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,54 +2668,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087277</v>
+        <v>121087312</v>
       </c>
       <c r="B19" t="n">
-        <v>97048</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,38 +2698,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541725</v>
+        <v>542080</v>
       </c>
       <c r="R19" t="n">
-        <v>7208037</v>
+        <v>7208265</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2772,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2782,7 +2780,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2809,10 +2807,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121087328</v>
+        <v>121087326</v>
       </c>
       <c r="B20" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2825,39 +2823,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541831</v>
+        <v>541877</v>
       </c>
       <c r="R20" t="n">
-        <v>7208060</v>
+        <v>7208115</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2889,7 +2882,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2899,7 +2892,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2926,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087294</v>
+        <v>121087502</v>
       </c>
       <c r="B21" t="n">
-        <v>90723</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2942,37 +2935,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541831</v>
+        <v>541613</v>
       </c>
       <c r="R21" t="n">
-        <v>7208244</v>
+        <v>7208020</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3001,7 +3002,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3011,7 +3012,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,22 +3027,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087343</v>
+        <v>121087327</v>
       </c>
       <c r="B22" t="n">
-        <v>82388</v>
+        <v>57504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3054,34 +3055,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541847</v>
+        <v>541871</v>
       </c>
       <c r="R22" t="n">
-        <v>7207905</v>
+        <v>7208138</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3113,7 +3118,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3123,7 +3128,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3150,7 +3155,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121087348</v>
+        <v>121086331</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -3184,24 +3189,27 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541837</v>
+        <v>541703</v>
       </c>
       <c r="R23" t="n">
-        <v>7207922</v>
+        <v>7208142</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3230,7 +3238,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3240,7 +3248,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,23 +3264,43 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121087237</v>
+        <v>121087336</v>
       </c>
       <c r="B24" t="n">
         <v>57351</v>
@@ -3301,27 +3334,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542031</v>
+        <v>541811</v>
       </c>
       <c r="R24" t="n">
-        <v>7208267</v>
+        <v>7208016</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3350,7 +3380,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3360,7 +3390,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,22 +3405,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121087278</v>
+        <v>121087310</v>
       </c>
       <c r="B25" t="n">
-        <v>97054</v>
+        <v>90710</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3399,25 +3429,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3427,10 +3457,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541725</v>
+        <v>542016</v>
       </c>
       <c r="R25" t="n">
-        <v>7208037</v>
+        <v>7208334</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3462,7 +3492,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3472,7 +3502,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3499,10 +3529,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121087284</v>
+        <v>121087319</v>
       </c>
       <c r="B26" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3515,34 +3545,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541684</v>
+        <v>541952</v>
       </c>
       <c r="R26" t="n">
-        <v>7208052</v>
+        <v>7208197</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3574,7 +3609,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3584,7 +3619,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3611,10 +3646,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121086342</v>
+        <v>121087337</v>
       </c>
       <c r="B27" t="n">
-        <v>90705</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3627,40 +3662,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542017</v>
+        <v>541811</v>
       </c>
       <c r="R27" t="n">
-        <v>7208282</v>
+        <v>7208016</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3689,7 +3721,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3699,12 +3731,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>på granstubbe</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3713,54 +3740,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121086336</v>
+        <v>121087333</v>
       </c>
       <c r="B28" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,45 +3774,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541937</v>
+        <v>541811</v>
       </c>
       <c r="R28" t="n">
-        <v>7208222</v>
+        <v>7208014</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3840,7 +3833,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3850,12 +3843,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3866,46 +3854,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121087287</v>
+        <v>121087281</v>
       </c>
       <c r="B29" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3918,39 +3886,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541743</v>
+        <v>541693</v>
       </c>
       <c r="R29" t="n">
-        <v>7208173</v>
+        <v>7208064</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3982,7 +3945,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3992,7 +3955,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4019,10 +3982,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121087279</v>
+        <v>121086336</v>
       </c>
       <c r="B30" t="n">
-        <v>78686</v>
+        <v>57351</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4035,37 +3998,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541703</v>
+        <v>541937</v>
       </c>
       <c r="R30" t="n">
-        <v>7208051</v>
+        <v>7208222</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4094,7 +4065,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4104,7 +4075,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4115,23 +4091,43 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121087288</v>
+        <v>121087351</v>
       </c>
       <c r="B31" t="n">
         <v>57351</v>
@@ -4176,10 +4172,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541752</v>
+        <v>541838</v>
       </c>
       <c r="R31" t="n">
-        <v>7208173</v>
+        <v>7207903</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4211,7 +4207,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4221,7 +4217,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4248,7 +4244,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121086331</v>
+        <v>121087287</v>
       </c>
       <c r="B32" t="n">
         <v>57351</v>
@@ -4282,27 +4278,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541703</v>
+        <v>541743</v>
       </c>
       <c r="R32" t="n">
-        <v>7208142</v>
+        <v>7208173</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4331,7 +4324,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4341,12 +4334,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4357,46 +4345,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121087281</v>
+        <v>121087314</v>
       </c>
       <c r="B33" t="n">
-        <v>74710</v>
+        <v>78604</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4409,21 +4377,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4433,10 +4401,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541693</v>
+        <v>542055</v>
       </c>
       <c r="R33" t="n">
-        <v>7208064</v>
+        <v>7208322</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4468,7 +4436,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4478,7 +4446,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4505,10 +4473,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121087329</v>
+        <v>121087331</v>
       </c>
       <c r="B34" t="n">
-        <v>90709</v>
+        <v>57351</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4521,34 +4489,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541819</v>
+        <v>541817</v>
       </c>
       <c r="R34" t="n">
-        <v>7208041</v>
+        <v>7208035</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4580,7 +4553,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4590,7 +4563,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4617,10 +4590,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121087290</v>
+        <v>121087276</v>
       </c>
       <c r="B35" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4633,34 +4606,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541818</v>
+        <v>541745</v>
       </c>
       <c r="R35" t="n">
-        <v>7208201</v>
+        <v>7207997</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4692,7 +4670,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4702,7 +4680,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4729,10 +4707,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121087351</v>
+        <v>121087342</v>
       </c>
       <c r="B36" t="n">
-        <v>57351</v>
+        <v>79714</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4741,43 +4719,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541838</v>
+        <v>541840</v>
       </c>
       <c r="R36" t="n">
-        <v>7207903</v>
+        <v>7207901</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4809,7 +4782,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4819,7 +4792,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4846,7 +4819,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121087354</v>
+        <v>121087346</v>
       </c>
       <c r="B37" t="n">
         <v>57351</v>
@@ -4891,10 +4864,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541832</v>
+        <v>541837</v>
       </c>
       <c r="R37" t="n">
-        <v>7207855</v>
+        <v>7207939</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4926,7 +4899,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4936,7 +4909,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4963,7 +4936,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121087502</v>
+        <v>121086337</v>
       </c>
       <c r="B38" t="n">
         <v>57351</v>
@@ -5007,17 +4980,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541613</v>
+        <v>541917</v>
       </c>
       <c r="R38" t="n">
-        <v>7208020</v>
+        <v>7208182</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5046,7 +5019,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5056,7 +5029,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5067,26 +5045,41 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121087283</v>
+        <v>121087282</v>
       </c>
       <c r="B39" t="n">
-        <v>90705</v>
+        <v>78604</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5099,21 +5092,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5123,10 +5116,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541684</v>
+        <v>541693</v>
       </c>
       <c r="R39" t="n">
-        <v>7208053</v>
+        <v>7208064</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5158,7 +5151,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5168,7 +5161,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5195,10 +5188,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121087333</v>
+        <v>121087352</v>
       </c>
       <c r="B40" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5211,21 +5204,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5235,10 +5228,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541811</v>
+        <v>541827</v>
       </c>
       <c r="R40" t="n">
-        <v>7208014</v>
+        <v>7207856</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5270,7 +5263,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5280,7 +5273,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5307,10 +5300,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121087323</v>
+        <v>121087353</v>
       </c>
       <c r="B41" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5323,16 +5316,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5343,7 +5336,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5352,10 +5345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541897</v>
+        <v>541829</v>
       </c>
       <c r="R41" t="n">
-        <v>7208135</v>
+        <v>7207857</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5387,7 +5380,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5397,7 +5390,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5424,7 +5417,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121087335</v>
+        <v>121087291</v>
       </c>
       <c r="B42" t="n">
         <v>57351</v>
@@ -5469,10 +5462,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541794</v>
+        <v>541832</v>
       </c>
       <c r="R42" t="n">
-        <v>7208008</v>
+        <v>7208226</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5504,7 +5497,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5514,7 +5507,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5541,10 +5534,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121087309</v>
+        <v>121087275</v>
       </c>
       <c r="B43" t="n">
-        <v>90995</v>
+        <v>57351</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5557,34 +5550,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542016</v>
+        <v>541756</v>
       </c>
       <c r="R43" t="n">
-        <v>7208333</v>
+        <v>7208000</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5616,7 +5614,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5626,7 +5624,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5653,10 +5651,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121086337</v>
+        <v>121087344</v>
       </c>
       <c r="B44" t="n">
-        <v>57351</v>
+        <v>77541</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5669,45 +5667,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541917</v>
+        <v>541846</v>
       </c>
       <c r="R44" t="n">
-        <v>7208182</v>
+        <v>7207904</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5736,7 +5726,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5746,12 +5736,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5762,38 +5747,23 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121087352</v>
+        <v>121087320</v>
       </c>
       <c r="B45" t="n">
         <v>78604</v>
@@ -5833,10 +5803,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541827</v>
+        <v>541956</v>
       </c>
       <c r="R45" t="n">
-        <v>7207856</v>
+        <v>7208191</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5868,7 +5838,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5878,7 +5848,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5905,7 +5875,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121087339</v>
+        <v>121086330</v>
       </c>
       <c r="B46" t="n">
         <v>57351</v>
@@ -5939,24 +5909,27 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541843</v>
+        <v>541697</v>
       </c>
       <c r="R46" t="n">
-        <v>7207891</v>
+        <v>7208101</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5985,7 +5958,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5995,7 +5968,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6006,23 +5984,43 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121087315</v>
+        <v>121087237</v>
       </c>
       <c r="B47" t="n">
         <v>57351</v>
@@ -6056,24 +6054,27 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>542012</v>
+        <v>542031</v>
       </c>
       <c r="R47" t="n">
-        <v>7208299</v>
+        <v>7208267</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6102,7 +6103,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6112,7 +6113,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6127,22 +6128,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121087337</v>
+        <v>121087277</v>
       </c>
       <c r="B48" t="n">
-        <v>78604</v>
+        <v>97049</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6151,25 +6152,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6179,10 +6180,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541811</v>
+        <v>541725</v>
       </c>
       <c r="R48" t="n">
-        <v>7208016</v>
+        <v>7208037</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6214,7 +6215,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6224,7 +6225,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6251,10 +6252,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121087332</v>
+        <v>121087318</v>
       </c>
       <c r="B49" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6267,34 +6268,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541817</v>
+        <v>541944</v>
       </c>
       <c r="R49" t="n">
-        <v>7208031</v>
+        <v>7208213</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6326,7 +6332,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6336,7 +6342,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6363,10 +6369,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121087345</v>
+        <v>121087294</v>
       </c>
       <c r="B50" t="n">
-        <v>74710</v>
+        <v>90724</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6379,21 +6385,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6403,10 +6409,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>541847</v>
+        <v>541831</v>
       </c>
       <c r="R50" t="n">
-        <v>7207903</v>
+        <v>7208244</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6438,7 +6444,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6448,7 +6454,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6475,10 +6481,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121087295</v>
+        <v>121087313</v>
       </c>
       <c r="B51" t="n">
-        <v>90709</v>
+        <v>79686</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6491,21 +6497,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6515,10 +6521,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>541831</v>
+        <v>542053</v>
       </c>
       <c r="R51" t="n">
-        <v>7208244</v>
+        <v>7208323</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6550,7 +6556,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6560,7 +6566,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6587,10 +6593,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121087320</v>
+        <v>121086341</v>
       </c>
       <c r="B52" t="n">
-        <v>78604</v>
+        <v>90706</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6603,37 +6609,40 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541956</v>
+        <v>541777</v>
       </c>
       <c r="R52" t="n">
-        <v>7208191</v>
+        <v>7207940</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6662,7 +6671,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6672,7 +6681,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6681,25 +6695,51 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121086334</v>
+        <v>121087293</v>
       </c>
       <c r="B53" t="n">
         <v>57351</v>
@@ -6733,27 +6773,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542045</v>
+        <v>541831</v>
       </c>
       <c r="R53" t="n">
-        <v>7208314</v>
+        <v>7208244</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6782,7 +6819,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6792,12 +6829,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6808,46 +6840,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121087314</v>
+        <v>121086335</v>
       </c>
       <c r="B54" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6860,37 +6872,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542055</v>
+        <v>541999</v>
       </c>
       <c r="R54" t="n">
-        <v>7208322</v>
+        <v>7208264</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6919,7 +6939,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6929,7 +6949,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6940,26 +6965,41 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121087353</v>
+        <v>121087284</v>
       </c>
       <c r="B55" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6972,39 +7012,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541829</v>
+        <v>541684</v>
       </c>
       <c r="R55" t="n">
-        <v>7207857</v>
+        <v>7208052</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7036,7 +7071,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7046,7 +7081,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7073,10 +7108,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121087275</v>
+        <v>121087355</v>
       </c>
       <c r="B56" t="n">
-        <v>57351</v>
+        <v>77945</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7085,43 +7120,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541756</v>
+        <v>541834</v>
       </c>
       <c r="R56" t="n">
-        <v>7208000</v>
+        <v>7207850</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7153,7 +7183,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7163,7 +7193,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7190,10 +7220,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121087327</v>
+        <v>121087357</v>
       </c>
       <c r="B57" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7206,38 +7236,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541871</v>
+        <v>541832</v>
       </c>
       <c r="R57" t="n">
-        <v>7208138</v>
+        <v>7207849</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7269,7 +7295,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7279,7 +7305,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7306,10 +7332,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121087334</v>
+        <v>121087317</v>
       </c>
       <c r="B58" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7322,39 +7348,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541801</v>
+        <v>541984</v>
       </c>
       <c r="R58" t="n">
-        <v>7208005</v>
+        <v>7208289</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7386,7 +7407,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7396,7 +7417,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7423,7 +7444,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121087291</v>
+        <v>121087321</v>
       </c>
       <c r="B59" t="n">
         <v>57351</v>
@@ -7459,7 +7480,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7468,10 +7489,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541832</v>
+        <v>541931</v>
       </c>
       <c r="R59" t="n">
-        <v>7208226</v>
+        <v>7208201</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7503,7 +7524,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7513,7 +7534,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7540,7 +7561,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121087276</v>
+        <v>121087334</v>
       </c>
       <c r="B60" t="n">
         <v>57351</v>
@@ -7576,7 +7597,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7585,10 +7606,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541745</v>
+        <v>541801</v>
       </c>
       <c r="R60" t="n">
-        <v>7207997</v>
+        <v>7208005</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7620,7 +7641,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7630,7 +7651,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7657,10 +7678,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121087344</v>
+        <v>121087283</v>
       </c>
       <c r="B61" t="n">
-        <v>77541</v>
+        <v>90706</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7673,21 +7694,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7697,10 +7718,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541846</v>
+        <v>541684</v>
       </c>
       <c r="R61" t="n">
-        <v>7207904</v>
+        <v>7208053</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7732,7 +7753,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7742,7 +7763,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7769,10 +7790,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121087322</v>
+        <v>121087311</v>
       </c>
       <c r="B62" t="n">
-        <v>78604</v>
+        <v>91054</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7781,25 +7802,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7809,10 +7830,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>541931</v>
+        <v>542016</v>
       </c>
       <c r="R62" t="n">
-        <v>7208192</v>
+        <v>7208338</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7844,7 +7865,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7854,7 +7875,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>S. brevispora s.str</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7865,6 +7891,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>ullticka</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7881,7 +7922,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121087341</v>
+        <v>121087280</v>
       </c>
       <c r="B63" t="n">
         <v>78604</v>
@@ -7921,10 +7962,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>541840</v>
+        <v>541704</v>
       </c>
       <c r="R63" t="n">
-        <v>7207901</v>
+        <v>7208050</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7956,7 +7997,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7966,7 +8007,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7993,10 +8034,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121087340</v>
+        <v>121087335</v>
       </c>
       <c r="B64" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8009,34 +8050,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>541843</v>
+        <v>541794</v>
       </c>
       <c r="R64" t="n">
-        <v>7207891</v>
+        <v>7208008</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8068,7 +8114,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8078,7 +8124,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8105,10 +8151,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121087326</v>
+        <v>121087324</v>
       </c>
       <c r="B65" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8121,34 +8167,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>541877</v>
+        <v>541881</v>
       </c>
       <c r="R65" t="n">
-        <v>7208115</v>
+        <v>7208125</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8217,7 +8268,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121087331</v>
+        <v>121087285</v>
       </c>
       <c r="B66" t="n">
         <v>57351</v>
@@ -8253,7 +8304,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8262,10 +8313,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541817</v>
+        <v>541686</v>
       </c>
       <c r="R66" t="n">
-        <v>7208035</v>
+        <v>7208061</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8297,7 +8348,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8307,7 +8358,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8334,10 +8385,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121087350</v>
+        <v>121087323</v>
       </c>
       <c r="B67" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8350,16 +8401,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8379,10 +8430,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541839</v>
+        <v>541897</v>
       </c>
       <c r="R67" t="n">
-        <v>7207908</v>
+        <v>7208135</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8414,7 +8465,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8424,7 +8475,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8451,10 +8502,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121087286</v>
+        <v>121087278</v>
       </c>
       <c r="B68" t="n">
-        <v>57351</v>
+        <v>97055</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8463,43 +8514,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541670</v>
+        <v>541725</v>
       </c>
       <c r="R68" t="n">
-        <v>7208095</v>
+        <v>7208037</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8531,7 +8577,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8541,7 +8587,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8568,10 +8614,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121087356</v>
+        <v>121087279</v>
       </c>
       <c r="B69" t="n">
-        <v>82388</v>
+        <v>78686</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8584,21 +8630,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8608,10 +8654,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541832</v>
+        <v>541703</v>
       </c>
       <c r="R69" t="n">
-        <v>7207849</v>
+        <v>7208051</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8643,7 +8689,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8653,7 +8699,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8680,10 +8726,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121087357</v>
+        <v>121087343</v>
       </c>
       <c r="B70" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8696,21 +8742,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8720,10 +8766,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541832</v>
+        <v>541847</v>
       </c>
       <c r="R70" t="n">
-        <v>7207849</v>
+        <v>7207905</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8755,7 +8801,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8765,7 +8811,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8792,10 +8838,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121087312</v>
+        <v>121087322</v>
       </c>
       <c r="B71" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8808,43 +8854,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>542080</v>
+        <v>541931</v>
       </c>
       <c r="R71" t="n">
-        <v>7208265</v>
+        <v>7208192</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8876,7 +8913,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8886,7 +8923,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8913,10 +8950,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121086330</v>
+        <v>121087340</v>
       </c>
       <c r="B72" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8929,45 +8966,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>541697</v>
+        <v>541843</v>
       </c>
       <c r="R72" t="n">
-        <v>7208101</v>
+        <v>7207891</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8996,7 +9025,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9006,12 +9035,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9022,46 +9046,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121087349</v>
+        <v>121086342</v>
       </c>
       <c r="B73" t="n">
-        <v>57351</v>
+        <v>90706</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9074,42 +9078,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541836</v>
+        <v>542017</v>
       </c>
       <c r="R73" t="n">
-        <v>7207921</v>
+        <v>7208282</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9138,7 +9140,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9148,7 +9150,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>på granstubbe</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9157,28 +9164,54 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121087319</v>
+        <v>121087356</v>
       </c>
       <c r="B74" t="n">
-        <v>57351</v>
+        <v>82388</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9191,39 +9224,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541952</v>
+        <v>541832</v>
       </c>
       <c r="R74" t="n">
-        <v>7208197</v>
+        <v>7207849</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9255,7 +9283,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9265,7 +9293,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9292,7 +9320,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121086335</v>
+        <v>121087339</v>
       </c>
       <c r="B75" t="n">
         <v>57351</v>
@@ -9326,27 +9354,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541999</v>
+        <v>541843</v>
       </c>
       <c r="R75" t="n">
-        <v>7208264</v>
+        <v>7207891</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9375,7 +9400,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9385,12 +9410,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9401,41 +9421,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121087336</v>
+        <v>121087290</v>
       </c>
       <c r="B76" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9448,39 +9453,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541811</v>
+        <v>541818</v>
       </c>
       <c r="R76" t="n">
-        <v>7208016</v>
+        <v>7208201</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
